--- a/Budgeting System_Expense Line Items.xlsx
+++ b/Budgeting System_Expense Line Items.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oclpholdings-my.sharepoint.com/personal/jumalonpvp_ortigas_com_ph/Documents/Desktop/AI Claude/Budgeting System/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oclpholdings-my.sharepoint.com/personal/jumalonpvp_ortigas_com_ph/Documents/Documents/Budgeting System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1153" documentId="8_{0783591E-5769-43D4-AE4C-AE389C7EA1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20CC5A8D-CEBB-41AE-B047-1C5997289FB4}"/>
+  <xr:revisionPtr revIDLastSave="1157" documentId="8_{0783591E-5769-43D4-AE4C-AE389C7EA1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FA03EB7-F7CD-4CB0-90E0-01FFA8D3E3F9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7D30BD04-AED0-48C4-A0F0-DC51EF4C24C2}"/>
   </bookViews>
@@ -1292,17 +1292,7 @@
     <cellStyle name="Percent 5" xfId="31" xr:uid="{57211BCC-76E5-4935-93C4-E945D92F0322}"/>
     <cellStyle name="Percent 6" xfId="34" xr:uid="{CCF8FCB8-15CB-47CA-BB20-07695FA6C5C7}"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1819,7 +1809,7 @@
     <col min="1" max="1" width="26.453125" customWidth="1"/>
     <col min="2" max="2" width="31.6328125" style="5" customWidth="1"/>
     <col min="3" max="3" width="15.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.453125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="40.453125" style="5" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="23.08984375" customWidth="1"/>
     <col min="6" max="6" width="22.08984375" customWidth="1"/>
     <col min="7" max="7" width="23.08984375" customWidth="1"/>
@@ -6219,59 +6209,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:I233" xr:uid="{0B1226CB-0107-4D8F-A599-9B58ED89F844}"/>
-  <conditionalFormatting sqref="B226:D1048576 B2:D219">
-    <cfRule type="duplicateValues" dxfId="18" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A143">
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A145">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A146">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A158">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A159">
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A103">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A104">
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A144">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A156:A157 A150">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A87">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A88">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A93">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3:A28">
-    <cfRule type="duplicateValues" dxfId="2" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A233">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="D226:D1048576 D2:D219">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Budgeting System_Expense Line Items.xlsx
+++ b/Budgeting System_Expense Line Items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jumalonpvp\Downloads\Budgeting System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C8EB5D-6DAA-42BB-918F-8C4F4D8C7AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E83D21-FB74-4341-AD16-447DBE30D6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7D30BD04-AED0-48C4-A0F0-DC51EF4C24C2}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2404" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2417" uniqueCount="504">
   <si>
     <t>Expense Line Item</t>
   </si>
@@ -1102,9 +1102,6 @@
     <t>Corporate Finance</t>
   </si>
   <si>
-    <t>Admin Services</t>
-  </si>
-  <si>
     <t>External Affairs</t>
   </si>
   <si>
@@ -1136,9 +1133,6 @@
   </si>
   <si>
     <t>Crowdstrike Endpoint Security</t>
-  </si>
-  <si>
-    <t>Budget</t>
   </si>
   <si>
     <t>Internet Connection</t>
@@ -2174,6 +2168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1226CB-0107-4D8F-A599-9B58ED89F844}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:R360"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2215,16 +2210,16 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C2" t="s">
         <v>450</v>
       </c>
-      <c r="B2" t="s">
-        <v>451</v>
-      </c>
-      <c r="C2" t="s">
-        <v>452</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>214</v>
@@ -2242,10 +2237,10 @@
         <v>28</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>24</v>
@@ -2288,18 +2283,18 @@
         <v>225</v>
       </c>
       <c r="F3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
       <c r="I3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L3">
         <v>81123102</v>
@@ -2317,7 +2312,7 @@
         <v>259</v>
       </c>
       <c r="R3" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -2345,13 +2340,13 @@
       <c r="G4"/>
       <c r="H4"/>
       <c r="I4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L4">
         <v>81123102</v>
@@ -2369,7 +2364,7 @@
         <v>259</v>
       </c>
       <c r="R4" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
@@ -2397,13 +2392,13 @@
       <c r="G5"/>
       <c r="H5"/>
       <c r="I5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L5">
         <v>81123102</v>
@@ -2421,7 +2416,7 @@
         <v>259</v>
       </c>
       <c r="R5" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -2441,7 +2436,7 @@
         <v>AS-27-4</v>
       </c>
       <c r="E6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -2451,13 +2446,13 @@
       </c>
       <c r="H6"/>
       <c r="I6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="L6">
         <v>81123102</v>
@@ -2466,10 +2461,10 @@
         <v>52951101</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="P6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -2489,7 +2484,7 @@
         <v>AS-27-5</v>
       </c>
       <c r="E7" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -2499,13 +2494,13 @@
       </c>
       <c r="H7"/>
       <c r="I7" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J7" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K7" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="L7">
         <v>80123102</v>
@@ -2514,10 +2509,10 @@
         <v>61721101</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="P7" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
@@ -2537,19 +2532,19 @@
         <v>AS-27-6</v>
       </c>
       <c r="E8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>276</v>
       </c>
       <c r="I8" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="L8">
         <v>80123102</v>
@@ -2575,19 +2570,19 @@
         <v>AS-27-7</v>
       </c>
       <c r="E9" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>277</v>
       </c>
       <c r="I9" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J9" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K9" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="L9">
         <v>80123102</v>
@@ -2613,7 +2608,7 @@
         <v>AS-27-8</v>
       </c>
       <c r="E10" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F10" t="s">
         <v>10</v>
@@ -2621,13 +2616,13 @@
       <c r="G10"/>
       <c r="H10"/>
       <c r="I10" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J10" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K10" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="L10">
         <v>80123102</v>
@@ -2639,7 +2634,7 @@
         <v>9</v>
       </c>
       <c r="R10" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
@@ -2667,13 +2662,13 @@
       <c r="G11"/>
       <c r="H11"/>
       <c r="I11" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J11" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K11" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L11">
         <v>81123102</v>
@@ -2691,7 +2686,7 @@
         <v>259</v>
       </c>
       <c r="R11" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
@@ -2719,13 +2714,13 @@
       <c r="G12"/>
       <c r="H12"/>
       <c r="I12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J12" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="K12" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L12">
         <v>80123102</v>
@@ -2734,7 +2729,7 @@
         <v>61711101</v>
       </c>
       <c r="R12" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
@@ -2762,13 +2757,13 @@
       <c r="G13"/>
       <c r="H13"/>
       <c r="I13" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J13" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="K13" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L13">
         <v>80123102</v>
@@ -2780,7 +2775,7 @@
         <v>249</v>
       </c>
       <c r="R13" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
@@ -2808,13 +2803,13 @@
       <c r="G14"/>
       <c r="H14"/>
       <c r="I14" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J14" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K14" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L14">
         <v>80123102</v>
@@ -2851,13 +2846,13 @@
       <c r="G15"/>
       <c r="H15"/>
       <c r="I15" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J15" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K15" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L15">
         <v>80123102</v>
@@ -2866,7 +2861,7 @@
         <v>61111201</v>
       </c>
       <c r="R15" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
@@ -2894,13 +2889,13 @@
       <c r="G16"/>
       <c r="H16"/>
       <c r="I16" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J16" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K16" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L16">
         <v>81123102</v>
@@ -2909,16 +2904,16 @@
         <v>52119101</v>
       </c>
       <c r="N16" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="O16" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="P16" t="s">
         <v>259</v>
       </c>
       <c r="R16" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.35">
@@ -2946,13 +2941,13 @@
       <c r="G17"/>
       <c r="H17"/>
       <c r="I17" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J17" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K17" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L17">
         <v>81123102</v>
@@ -2970,7 +2965,7 @@
         <v>259</v>
       </c>
       <c r="R17" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.35">
@@ -2998,13 +2993,13 @@
       <c r="G18"/>
       <c r="H18"/>
       <c r="I18" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J18" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K18" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L18">
         <v>81123102</v>
@@ -3044,13 +3039,13 @@
       <c r="G19"/>
       <c r="H19"/>
       <c r="I19" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J19" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K19" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L19">
         <v>81123102</v>
@@ -3090,13 +3085,13 @@
       <c r="G20"/>
       <c r="H20"/>
       <c r="I20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J20" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="K20" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L20">
         <v>80123102</v>
@@ -3114,7 +3109,7 @@
         <v>260</v>
       </c>
       <c r="R20" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.35">
@@ -3142,13 +3137,13 @@
       <c r="G21"/>
       <c r="H21"/>
       <c r="I21" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J21" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K21" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L21">
         <v>81123102</v>
@@ -3185,13 +3180,13 @@
       <c r="G22"/>
       <c r="H22"/>
       <c r="I22" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J22" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K22" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L22">
         <v>81123102</v>
@@ -3223,13 +3218,13 @@
         <v>278</v>
       </c>
       <c r="I23" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J23" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K23" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L23">
         <v>80123102</v>
@@ -3263,13 +3258,13 @@
       <c r="G24"/>
       <c r="H24"/>
       <c r="I24" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J24" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="K24" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L24">
         <v>80123102</v>
@@ -3278,7 +3273,7 @@
         <v>61071099</v>
       </c>
       <c r="R24" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.35">
@@ -3301,18 +3296,18 @@
         <v>298</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G25"/>
       <c r="H25"/>
       <c r="I25" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J25" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K25" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L25">
         <v>81123102</v>
@@ -3346,13 +3341,13 @@
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J26" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K26" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L26">
         <v>81123102</v>
@@ -3384,18 +3379,18 @@
         <v>298</v>
       </c>
       <c r="F27" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G27"/>
       <c r="H27"/>
       <c r="I27" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J27" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K27" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L27">
         <v>81123102</v>
@@ -3432,13 +3427,13 @@
       <c r="G28"/>
       <c r="H28"/>
       <c r="I28" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J28" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K28" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L28">
         <v>81123102</v>
@@ -3450,7 +3445,7 @@
         <v>249</v>
       </c>
       <c r="Q28" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.35">
@@ -3473,18 +3468,18 @@
         <v>298</v>
       </c>
       <c r="F29" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G29"/>
       <c r="H29"/>
       <c r="I29" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J29" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K29" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L29">
         <v>80123102</v>
@@ -3518,13 +3513,13 @@
       <c r="G30"/>
       <c r="H30"/>
       <c r="I30" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J30" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K30" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L30">
         <v>80123102</v>
@@ -3533,10 +3528,10 @@
         <v>61061104</v>
       </c>
       <c r="N30" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="O30" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="P30" t="s">
         <v>259</v>
@@ -3567,13 +3562,13 @@
       <c r="G31"/>
       <c r="H31"/>
       <c r="I31" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J31" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K31" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L31">
         <v>81123102</v>
@@ -3591,7 +3586,7 @@
         <v>259</v>
       </c>
       <c r="R31" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.35">
@@ -3619,13 +3614,13 @@
       <c r="G32"/>
       <c r="H32"/>
       <c r="I32" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J32" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K32" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L32">
         <v>81123102</v>
@@ -3634,7 +3629,7 @@
         <v>52081101</v>
       </c>
       <c r="R32" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.35">
@@ -3662,13 +3657,13 @@
       <c r="G33"/>
       <c r="H33"/>
       <c r="I33" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J33" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K33" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L33">
         <v>81123102</v>
@@ -3677,7 +3672,7 @@
         <v>52081101</v>
       </c>
       <c r="R33" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.35">
@@ -3700,16 +3695,16 @@
         <v>262</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I34" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J34" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K34" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L34" s="9">
         <v>80123102</v>
@@ -3743,13 +3738,13 @@
       <c r="G35"/>
       <c r="H35"/>
       <c r="I35" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J35" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="K35" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L35">
         <v>80123102</v>
@@ -3758,19 +3753,19 @@
         <v>61061104</v>
       </c>
       <c r="N35" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="O35" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="P35" t="s">
         <v>260</v>
       </c>
       <c r="R35" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="str">
         <f>_xlfn.XLOOKUP(I36,Lookup!A:A,Lookup!B:B)</f>
         <v>BCA</v>
@@ -3790,16 +3785,16 @@
         <v>264</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I36" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L36">
         <v>80134103</v>
@@ -3808,7 +3803,7 @@
         <v>61711101</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="str">
         <f>_xlfn.XLOOKUP(I37,Lookup!A:A,Lookup!B:B)</f>
         <v>BCA</v>
@@ -3825,19 +3820,19 @@
         <v>BCA-27-35</v>
       </c>
       <c r="E37" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="I37" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L37">
         <v>80134103</v>
@@ -3846,7 +3841,7 @@
         <v>61901109</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="str">
         <f>_xlfn.XLOOKUP(I38,Lookup!A:A,Lookup!B:B)</f>
         <v>BCA</v>
@@ -3863,19 +3858,19 @@
         <v>BCA-27-36</v>
       </c>
       <c r="E38" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I38" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L38">
         <v>81123102</v>
@@ -3884,7 +3879,7 @@
         <v>52041502</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="str">
         <f>_xlfn.XLOOKUP(I39,Lookup!A:A,Lookup!B:B)</f>
         <v>BCA</v>
@@ -3901,19 +3896,19 @@
         <v>BCA-27-37</v>
       </c>
       <c r="E39" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="I39" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L39">
         <v>80123102</v>
@@ -3922,7 +3917,7 @@
         <v>61961302</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="str">
         <f>_xlfn.XLOOKUP(I40,Lookup!A:A,Lookup!B:B)</f>
         <v>BCA</v>
@@ -3939,22 +3934,22 @@
         <v>BCA-27-38</v>
       </c>
       <c r="E40" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F40" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>220</v>
       </c>
       <c r="I40" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L40">
         <v>80111101</v>
@@ -3962,8 +3957,11 @@
       <c r="M40">
         <v>61021317</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R40" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="str">
         <f>_xlfn.XLOOKUP(I41,Lookup!A:A,Lookup!B:B)</f>
         <v>BCA</v>
@@ -3980,22 +3978,22 @@
         <v>BCA-27-39</v>
       </c>
       <c r="E41" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F41" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>219</v>
       </c>
       <c r="I41" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L41">
         <v>81111101</v>
@@ -4003,8 +4001,11 @@
       <c r="M41">
         <v>52121316</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="str">
         <f>_xlfn.XLOOKUP(I42,Lookup!A:A,Lookup!B:B)</f>
         <v>BCA</v>
@@ -4021,22 +4022,22 @@
         <v>BCA-27-40</v>
       </c>
       <c r="E42" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F42" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>221</v>
       </c>
       <c r="I42" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L42">
         <v>90111101</v>
@@ -4044,8 +4045,11 @@
       <c r="M42">
         <v>52121316</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="str">
         <f>_xlfn.XLOOKUP(I43,Lookup!A:A,Lookup!B:B)</f>
         <v>BCA</v>
@@ -4067,13 +4071,13 @@
         <v>301</v>
       </c>
       <c r="I43" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L43">
         <v>80349101</v>
@@ -4081,11 +4085,8 @@
       <c r="M43">
         <v>61959994</v>
       </c>
-      <c r="R43" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="str">
         <f>_xlfn.XLOOKUP(I44,Lookup!A:A,Lookup!B:B)</f>
         <v>BCA</v>
@@ -4105,16 +4106,16 @@
         <v>306</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I44" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L44">
         <v>80349101</v>
@@ -4123,7 +4124,7 @@
         <v>61959994</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="str">
         <f>_xlfn.XLOOKUP(I45,Lookup!A:A,Lookup!B:B)</f>
         <v>BCA</v>
@@ -4146,13 +4147,13 @@
         <v>307</v>
       </c>
       <c r="I45" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L45">
         <v>81349101</v>
@@ -4160,11 +4161,8 @@
       <c r="M45">
         <v>52959901</v>
       </c>
-      <c r="R45" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="str">
         <f>_xlfn.XLOOKUP(I46,Lookup!A:A,Lookup!B:B)</f>
         <v>BCA</v>
@@ -4187,13 +4185,13 @@
         <v>302</v>
       </c>
       <c r="I46" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L46">
         <v>81349101</v>
@@ -4201,11 +4199,8 @@
       <c r="M46">
         <v>52959901</v>
       </c>
-      <c r="R46" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="str">
         <f>_xlfn.XLOOKUP(I47,Lookup!A:A,Lookup!B:B)</f>
         <v>BCA</v>
@@ -4228,13 +4223,13 @@
         <v>304</v>
       </c>
       <c r="I47" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L47">
         <v>80349101</v>
@@ -4242,11 +4237,8 @@
       <c r="M47">
         <v>61959994</v>
       </c>
-      <c r="R47" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="str">
         <f>_xlfn.XLOOKUP(I48,Lookup!A:A,Lookup!B:B)</f>
         <v>BCA</v>
@@ -4269,13 +4261,13 @@
         <v>305</v>
       </c>
       <c r="I48" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L48">
         <v>81222101</v>
@@ -4283,11 +4275,8 @@
       <c r="M48">
         <v>61959994</v>
       </c>
-      <c r="R48" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="str">
         <f>_xlfn.XLOOKUP(I49,Lookup!A:A,Lookup!B:B)</f>
         <v>BCA</v>
@@ -4310,13 +4299,13 @@
         <v>303</v>
       </c>
       <c r="I49" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L49">
         <v>81349101</v>
@@ -4324,11 +4313,8 @@
       <c r="M49">
         <v>52959901</v>
       </c>
-      <c r="R49" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="str">
         <f>_xlfn.XLOOKUP(I50,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -4353,10 +4339,10 @@
         <v>351</v>
       </c>
       <c r="J50" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K50" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L50">
         <v>90134102</v>
@@ -4368,7 +4354,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="str">
         <f>_xlfn.XLOOKUP(I51,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -4394,10 +4380,10 @@
         <v>351</v>
       </c>
       <c r="J51" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K51" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L51">
         <v>90134102</v>
@@ -4409,7 +4395,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="str">
         <f>_xlfn.XLOOKUP(I52,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -4439,10 +4425,10 @@
         <v>351</v>
       </c>
       <c r="J52" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K52" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L52">
         <v>90111101</v>
@@ -4454,7 +4440,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="str">
         <f>_xlfn.XLOOKUP(I53,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -4474,7 +4460,7 @@
         <v>264</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>219</v>
@@ -4483,10 +4469,10 @@
         <v>351</v>
       </c>
       <c r="J53" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K53" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L53">
         <v>81134102</v>
@@ -4495,7 +4481,7 @@
         <v>52952101</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="str">
         <f>_xlfn.XLOOKUP(I54,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -4515,7 +4501,7 @@
         <v>264</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>221</v>
@@ -4524,10 +4510,10 @@
         <v>351</v>
       </c>
       <c r="J54" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K54" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L54">
         <v>90134102</v>
@@ -4536,7 +4522,7 @@
         <v>52952101</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="str">
         <f>_xlfn.XLOOKUP(I55,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -4565,10 +4551,10 @@
         <v>351</v>
       </c>
       <c r="J55" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K55" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L55">
         <v>80134102</v>
@@ -4580,7 +4566,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="str">
         <f>_xlfn.XLOOKUP(I56,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -4609,10 +4595,10 @@
         <v>351</v>
       </c>
       <c r="J56" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K56" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L56">
         <v>81134102</v>
@@ -4624,7 +4610,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="str">
         <f>_xlfn.XLOOKUP(I57,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -4653,10 +4639,10 @@
         <v>351</v>
       </c>
       <c r="J57" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K57" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L57">
         <v>90134102</v>
@@ -4668,7 +4654,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="str">
         <f>_xlfn.XLOOKUP(I58,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -4697,10 +4683,10 @@
         <v>351</v>
       </c>
       <c r="J58" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K58" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L58">
         <v>80134102</v>
@@ -4712,7 +4698,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="str">
         <f>_xlfn.XLOOKUP(I59,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -4741,10 +4727,10 @@
         <v>351</v>
       </c>
       <c r="J59" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K59" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L59">
         <v>81134102</v>
@@ -4756,7 +4742,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="str">
         <f>_xlfn.XLOOKUP(I60,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -4785,10 +4771,10 @@
         <v>351</v>
       </c>
       <c r="J60" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K60" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L60">
         <v>90134102</v>
@@ -4800,7 +4786,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="str">
         <f>_xlfn.XLOOKUP(I61,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -4829,10 +4815,10 @@
         <v>351</v>
       </c>
       <c r="J61" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K61" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L61">
         <v>90134102</v>
@@ -4844,7 +4830,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="str">
         <f>_xlfn.XLOOKUP(I62,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -4873,10 +4859,10 @@
         <v>351</v>
       </c>
       <c r="J62" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K62" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L62">
         <v>80134102</v>
@@ -4884,8 +4870,11 @@
       <c r="M62">
         <v>61071001</v>
       </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R62" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="str">
         <f>_xlfn.XLOOKUP(I63,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -4911,10 +4900,10 @@
         <v>351</v>
       </c>
       <c r="J63" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K63" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L63">
         <v>90111101</v>
@@ -4926,7 +4915,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="str">
         <f>_xlfn.XLOOKUP(I64,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -4952,10 +4941,10 @@
         <v>351</v>
       </c>
       <c r="J64" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K64" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L64">
         <v>90111101</v>
@@ -4967,7 +4956,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="str">
         <f>_xlfn.XLOOKUP(I65,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -4996,10 +4985,10 @@
         <v>351</v>
       </c>
       <c r="J65" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K65" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L65">
         <v>80111101</v>
@@ -5011,7 +5000,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="str">
         <f>_xlfn.XLOOKUP(I66,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -5040,10 +5029,10 @@
         <v>351</v>
       </c>
       <c r="J66" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K66" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L66">
         <v>81111101</v>
@@ -5055,7 +5044,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="str">
         <f>_xlfn.XLOOKUP(I67,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -5084,10 +5073,10 @@
         <v>351</v>
       </c>
       <c r="J67" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K67" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L67">
         <v>80111101</v>
@@ -5099,7 +5088,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="str">
         <f>_xlfn.XLOOKUP(I68,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -5128,10 +5117,10 @@
         <v>351</v>
       </c>
       <c r="J68" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K68" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L68">
         <v>81111101</v>
@@ -5143,7 +5132,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="str">
         <f>_xlfn.XLOOKUP(I69,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -5169,10 +5158,10 @@
         <v>351</v>
       </c>
       <c r="J69" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K69" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L69">
         <v>81111101</v>
@@ -5184,7 +5173,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="str">
         <f>_xlfn.XLOOKUP(I70,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -5210,10 +5199,10 @@
         <v>351</v>
       </c>
       <c r="J70" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K70" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L70">
         <v>81111101</v>
@@ -5225,7 +5214,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="str">
         <f>_xlfn.XLOOKUP(I71,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -5254,10 +5243,10 @@
         <v>351</v>
       </c>
       <c r="J71" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K71" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L71">
         <v>80111101</v>
@@ -5269,7 +5258,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="str">
         <f>_xlfn.XLOOKUP(I72,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -5298,10 +5287,10 @@
         <v>351</v>
       </c>
       <c r="J72" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K72" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L72">
         <v>81111101</v>
@@ -5313,7 +5302,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="str">
         <f>_xlfn.XLOOKUP(I73,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -5342,10 +5331,10 @@
         <v>351</v>
       </c>
       <c r="J73" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K73" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L73">
         <v>90111101</v>
@@ -5357,7 +5346,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="str">
         <f>_xlfn.XLOOKUP(I74,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -5374,19 +5363,19 @@
         <v>CF-27-25</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="I74" t="s">
         <v>351</v>
       </c>
       <c r="J74" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K74" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L74">
         <v>90134102</v>
@@ -5395,7 +5384,7 @@
         <v>52041494</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="str">
         <f>_xlfn.XLOOKUP(I75,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -5412,19 +5401,19 @@
         <v>CF-27-26</v>
       </c>
       <c r="E75" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="F75" s="5" t="s">
         <v>482</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>484</v>
       </c>
       <c r="I75" t="s">
         <v>351</v>
       </c>
       <c r="J75" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K75" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L75">
         <v>90134102</v>
@@ -5433,7 +5422,7 @@
         <v>52041494</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="str">
         <f>_xlfn.XLOOKUP(I76,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -5453,7 +5442,7 @@
         <v>247</v>
       </c>
       <c r="F76" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G76" t="s">
         <v>219</v>
@@ -5463,10 +5452,10 @@
         <v>351</v>
       </c>
       <c r="J76" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K76" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L76">
         <v>81134102</v>
@@ -5478,7 +5467,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="str">
         <f>_xlfn.XLOOKUP(I77,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -5504,10 +5493,10 @@
         <v>351</v>
       </c>
       <c r="J77" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K77" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L77">
         <v>80134102</v>
@@ -5519,7 +5508,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="str">
         <f>_xlfn.XLOOKUP(I78,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -5545,10 +5534,10 @@
         <v>351</v>
       </c>
       <c r="J78" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K78" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L78">
         <v>80134102</v>
@@ -5560,7 +5549,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="str">
         <f>_xlfn.XLOOKUP(I79,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -5586,10 +5575,10 @@
         <v>351</v>
       </c>
       <c r="J79" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K79" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L79">
         <v>80134102</v>
@@ -5601,7 +5590,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="str">
         <f>_xlfn.XLOOKUP(I80,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -5621,16 +5610,16 @@
         <v>313</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="I80" t="s">
         <v>351</v>
       </c>
       <c r="J80" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K80" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L80">
         <v>80134102</v>
@@ -5638,8 +5627,11 @@
       <c r="M80">
         <v>61711101</v>
       </c>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R80" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="str">
         <f>_xlfn.XLOOKUP(I81,Lookup!A:A,Lookup!B:B)</f>
         <v>CM</v>
@@ -5666,10 +5658,10 @@
         <v>165</v>
       </c>
       <c r="J81" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K81" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L81">
         <v>81314101</v>
@@ -5681,7 +5673,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="str">
         <f>_xlfn.XLOOKUP(I82,Lookup!A:A,Lookup!B:B)</f>
         <v>CM</v>
@@ -5709,10 +5701,10 @@
         <v>165</v>
       </c>
       <c r="J82" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K82" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L82">
         <v>81314101</v>
@@ -5724,7 +5716,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="str">
         <f>_xlfn.XLOOKUP(I83,Lookup!A:A,Lookup!B:B)</f>
         <v>CM</v>
@@ -5752,10 +5744,10 @@
         <v>165</v>
       </c>
       <c r="J83" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K83" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L83">
         <v>81314101</v>
@@ -5767,7 +5759,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="str">
         <f>_xlfn.XLOOKUP(I84,Lookup!A:A,Lookup!B:B)</f>
         <v>CM</v>
@@ -5795,10 +5787,10 @@
         <v>165</v>
       </c>
       <c r="J84" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K84" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L84">
         <v>81314101</v>
@@ -5810,7 +5802,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="str">
         <f>_xlfn.XLOOKUP(I85,Lookup!A:A,Lookup!B:B)</f>
         <v>CM</v>
@@ -5838,10 +5830,10 @@
         <v>165</v>
       </c>
       <c r="J85" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K85" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L85">
         <v>81314101</v>
@@ -5853,7 +5845,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="str">
         <f>_xlfn.XLOOKUP(I86,Lookup!A:A,Lookup!B:B)</f>
         <v>CM</v>
@@ -5881,10 +5873,10 @@
         <v>165</v>
       </c>
       <c r="J86" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K86" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L86">
         <v>81314101</v>
@@ -5896,7 +5888,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="str">
         <f>_xlfn.XLOOKUP(I87,Lookup!A:A,Lookup!B:B)</f>
         <v>CM</v>
@@ -5924,10 +5916,10 @@
         <v>165</v>
       </c>
       <c r="J87" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K87" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L87">
         <v>81314101</v>
@@ -5939,7 +5931,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="str">
         <f>_xlfn.XLOOKUP(I88,Lookup!A:A,Lookup!B:B)</f>
         <v>CM</v>
@@ -5967,10 +5959,10 @@
         <v>165</v>
       </c>
       <c r="J88" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K88" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L88">
         <v>81314101</v>
@@ -5982,7 +5974,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="str">
         <f>_xlfn.XLOOKUP(I89,Lookup!A:A,Lookup!B:B)</f>
         <v>CM</v>
@@ -6010,10 +6002,10 @@
         <v>165</v>
       </c>
       <c r="J89" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K89" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L89">
         <v>81314101</v>
@@ -6025,7 +6017,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="str">
         <f>_xlfn.XLOOKUP(I90,Lookup!A:A,Lookup!B:B)</f>
         <v>EA</v>
@@ -6041,22 +6033,22 @@
         <v>EA-27-1</v>
       </c>
       <c r="E90" t="s">
+        <v>353</v>
+      </c>
+      <c r="F90" s="5" t="s">
         <v>354</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>355</v>
       </c>
       <c r="G90" s="5" t="s">
         <v>220</v>
       </c>
       <c r="I90" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J90" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K90" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="L90">
         <v>80125101</v>
@@ -6065,7 +6057,7 @@
         <v>61959102</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="str">
         <f>_xlfn.XLOOKUP(I91,Lookup!A:A,Lookup!B:B)</f>
         <v>EA</v>
@@ -6082,22 +6074,22 @@
         <v>EA-27-2</v>
       </c>
       <c r="E91" t="s">
+        <v>353</v>
+      </c>
+      <c r="F91" s="5" t="s">
         <v>354</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>355</v>
       </c>
       <c r="G91" s="5" t="s">
         <v>219</v>
       </c>
       <c r="I91" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J91" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K91" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="L91">
         <v>81125101</v>
@@ -6106,7 +6098,7 @@
         <v>52959903</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="str">
         <f>_xlfn.XLOOKUP(I92,Lookup!A:A,Lookup!B:B)</f>
         <v>EA</v>
@@ -6123,22 +6115,22 @@
         <v>EA-27-3</v>
       </c>
       <c r="E92" t="s">
+        <v>353</v>
+      </c>
+      <c r="F92" s="5" t="s">
         <v>354</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>355</v>
       </c>
       <c r="G92" s="5" t="s">
         <v>221</v>
       </c>
       <c r="I92" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J92" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K92" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="L92">
         <v>90125101</v>
@@ -6147,7 +6139,7 @@
         <v>61959102</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:18" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="str">
         <f>_xlfn.XLOOKUP(I93,Lookup!A:A,Lookup!B:B)</f>
         <v>EA</v>
@@ -6164,19 +6156,19 @@
         <v>EA-27-4</v>
       </c>
       <c r="E93" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I93" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J93" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K93" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="L93">
         <v>80125101</v>
@@ -6184,11 +6176,8 @@
       <c r="M93">
         <v>61959102</v>
       </c>
-      <c r="R93" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="str">
         <f>_xlfn.XLOOKUP(I94,Lookup!A:A,Lookup!B:B)</f>
         <v>EA</v>
@@ -6208,19 +6197,19 @@
         <v>289</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G94" s="5" t="s">
         <v>220</v>
       </c>
       <c r="I94" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J94" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K94" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="L94">
         <v>80125101</v>
@@ -6229,7 +6218,7 @@
         <v>61091101</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="str">
         <f>_xlfn.XLOOKUP(I95,Lookup!A:A,Lookup!B:B)</f>
         <v>EA</v>
@@ -6249,19 +6238,19 @@
         <v>289</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>219</v>
       </c>
       <c r="I95" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J95" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K95" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="L95">
         <v>81125101</v>
@@ -6270,7 +6259,7 @@
         <v>52091101</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="str">
         <f>_xlfn.XLOOKUP(I96,Lookup!A:A,Lookup!B:B)</f>
         <v>EA</v>
@@ -6290,19 +6279,19 @@
         <v>289</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G96" s="5" t="s">
         <v>221</v>
       </c>
       <c r="I96" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J96" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K96" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="L96">
         <v>90125101</v>
@@ -6311,7 +6300,7 @@
         <v>61091101</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="str">
         <f>_xlfn.XLOOKUP(I97,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -6338,10 +6327,10 @@
         <v>84</v>
       </c>
       <c r="J97" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K97" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L97">
         <v>81122101</v>
@@ -6353,7 +6342,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="str">
         <f>_xlfn.XLOOKUP(I98,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -6381,10 +6370,10 @@
         <v>84</v>
       </c>
       <c r="J98" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K98" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L98">
         <v>81122101</v>
@@ -6396,7 +6385,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="str">
         <f>_xlfn.XLOOKUP(I99,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -6424,10 +6413,10 @@
         <v>84</v>
       </c>
       <c r="J99" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K99" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L99">
         <v>81122101</v>
@@ -6439,7 +6428,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="str">
         <f>_xlfn.XLOOKUP(I100,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -6467,10 +6456,10 @@
         <v>84</v>
       </c>
       <c r="J100" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K100" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L100">
         <v>81122101</v>
@@ -6482,7 +6471,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="str">
         <f>_xlfn.XLOOKUP(I101,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -6510,10 +6499,10 @@
         <v>84</v>
       </c>
       <c r="J101" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K101" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L101">
         <v>81122101</v>
@@ -6525,7 +6514,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="str">
         <f>_xlfn.XLOOKUP(I102,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -6553,10 +6542,10 @@
         <v>84</v>
       </c>
       <c r="J102" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K102" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L102">
         <v>81122101</v>
@@ -6568,7 +6557,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="str">
         <f>_xlfn.XLOOKUP(I103,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -6596,10 +6585,10 @@
         <v>84</v>
       </c>
       <c r="J103" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K103" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L103">
         <v>81122101</v>
@@ -6611,7 +6600,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="str">
         <f>_xlfn.XLOOKUP(I104,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -6639,10 +6628,10 @@
         <v>84</v>
       </c>
       <c r="J104" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K104" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L104">
         <v>81122101</v>
@@ -6654,7 +6643,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="str">
         <f>_xlfn.XLOOKUP(I105,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -6674,7 +6663,7 @@
         <v>215</v>
       </c>
       <c r="F105" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G105"/>
       <c r="H105"/>
@@ -6682,10 +6671,10 @@
         <v>84</v>
       </c>
       <c r="J105" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K105" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L105">
         <v>81122101</v>
@@ -6697,7 +6686,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="str">
         <f>_xlfn.XLOOKUP(I106,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -6725,10 +6714,10 @@
         <v>84</v>
       </c>
       <c r="J106" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K106" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L106">
         <v>81122101</v>
@@ -6740,7 +6729,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="str">
         <f>_xlfn.XLOOKUP(I107,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -6768,10 +6757,10 @@
         <v>84</v>
       </c>
       <c r="J107" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K107" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L107">
         <v>81122101</v>
@@ -6783,7 +6772,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="str">
         <f>_xlfn.XLOOKUP(I108,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -6811,10 +6800,10 @@
         <v>84</v>
       </c>
       <c r="J108" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K108" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L108">
         <v>81122101</v>
@@ -6826,7 +6815,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="str">
         <f>_xlfn.XLOOKUP(I109,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -6854,10 +6843,10 @@
         <v>84</v>
       </c>
       <c r="J109" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K109" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L109">
         <v>81122101</v>
@@ -6869,7 +6858,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="str">
         <f>_xlfn.XLOOKUP(I110,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -6897,10 +6886,10 @@
         <v>84</v>
       </c>
       <c r="J110" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K110" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L110">
         <v>81122101</v>
@@ -6912,7 +6901,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="str">
         <f>_xlfn.XLOOKUP(I111,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -6940,10 +6929,10 @@
         <v>84</v>
       </c>
       <c r="J111" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K111" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L111">
         <v>81122101</v>
@@ -6955,7 +6944,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="str">
         <f>_xlfn.XLOOKUP(I112,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -6983,10 +6972,10 @@
         <v>84</v>
       </c>
       <c r="J112" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K112" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L112">
         <v>81122101</v>
@@ -6998,7 +6987,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="str">
         <f>_xlfn.XLOOKUP(I113,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7026,10 +7015,10 @@
         <v>84</v>
       </c>
       <c r="J113" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K113" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L113">
         <v>81122101</v>
@@ -7041,7 +7030,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="str">
         <f>_xlfn.XLOOKUP(I114,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7069,10 +7058,10 @@
         <v>84</v>
       </c>
       <c r="J114" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K114" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L114">
         <v>81122101</v>
@@ -7084,7 +7073,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="str">
         <f>_xlfn.XLOOKUP(I115,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7112,10 +7101,10 @@
         <v>84</v>
       </c>
       <c r="J115" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K115" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L115">
         <v>81122101</v>
@@ -7127,7 +7116,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="str">
         <f>_xlfn.XLOOKUP(I116,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7155,10 +7144,10 @@
         <v>84</v>
       </c>
       <c r="J116" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K116" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L116">
         <v>90122101</v>
@@ -7170,7 +7159,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="str">
         <f>_xlfn.XLOOKUP(I117,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7198,10 +7187,10 @@
         <v>84</v>
       </c>
       <c r="J117" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K117" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L117">
         <v>90122101</v>
@@ -7213,7 +7202,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" t="str">
         <f>_xlfn.XLOOKUP(I118,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7241,10 +7230,10 @@
         <v>84</v>
       </c>
       <c r="J118" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K118" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L118">
         <v>81122101</v>
@@ -7253,10 +7242,10 @@
         <v>52121402</v>
       </c>
       <c r="N118" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="O118" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P118" t="s">
         <v>259</v>
@@ -7265,7 +7254,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" t="str">
         <f>_xlfn.XLOOKUP(I119,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7293,10 +7282,10 @@
         <v>84</v>
       </c>
       <c r="J119" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K119" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L119">
         <v>81122101</v>
@@ -7308,7 +7297,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="str">
         <f>_xlfn.XLOOKUP(I120,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7328,7 +7317,7 @@
         <v>268</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4"/>
@@ -7336,10 +7325,10 @@
         <v>84</v>
       </c>
       <c r="J120" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K120" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L120">
         <v>81122101</v>
@@ -7348,19 +7337,19 @@
         <v>52121402</v>
       </c>
       <c r="N120" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="O120" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P120" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="R120" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" t="str">
         <f>_xlfn.XLOOKUP(I121,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7388,10 +7377,10 @@
         <v>84</v>
       </c>
       <c r="J121" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K121" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L121">
         <v>81122101</v>
@@ -7400,19 +7389,19 @@
         <v>52121402</v>
       </c>
       <c r="N121" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="O121" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="P121" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="R121" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="str">
         <f>_xlfn.XLOOKUP(I122,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7442,10 +7431,10 @@
         <v>84</v>
       </c>
       <c r="J122" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K122" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L122">
         <v>90122101</v>
@@ -7454,19 +7443,19 @@
         <v>52121310</v>
       </c>
       <c r="N122" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="O122" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P122" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="R122" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="str">
         <f>_xlfn.XLOOKUP(I123,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7496,10 +7485,10 @@
         <v>84</v>
       </c>
       <c r="J123" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K123" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L123">
         <v>81122101</v>
@@ -7508,19 +7497,19 @@
         <v>52121310</v>
       </c>
       <c r="N123" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="O123" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P123" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="R123" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="str">
         <f>_xlfn.XLOOKUP(I124,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7550,10 +7539,10 @@
         <v>84</v>
       </c>
       <c r="J124" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K124" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L124">
         <v>80122101</v>
@@ -7562,19 +7551,19 @@
         <v>61021311</v>
       </c>
       <c r="N124" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="O124" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P124" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="R124" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="str">
         <f>_xlfn.XLOOKUP(I125,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7594,7 +7583,7 @@
         <v>268</v>
       </c>
       <c r="F125" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="G125"/>
       <c r="H125"/>
@@ -7602,10 +7591,10 @@
         <v>84</v>
       </c>
       <c r="J125" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K125" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L125">
         <v>81122101</v>
@@ -7614,10 +7603,10 @@
         <v>52121402</v>
       </c>
       <c r="N125" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="O125" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P125" t="s">
         <v>259</v>
@@ -7626,7 +7615,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="str">
         <f>_xlfn.XLOOKUP(I126,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7646,7 +7635,7 @@
         <v>268</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
@@ -7654,10 +7643,10 @@
         <v>84</v>
       </c>
       <c r="J126" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K126" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L126">
         <v>81122101</v>
@@ -7666,10 +7655,10 @@
         <v>52121402</v>
       </c>
       <c r="N126" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="O126" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="P126" t="s">
         <v>259</v>
@@ -7678,7 +7667,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="str">
         <f>_xlfn.XLOOKUP(I127,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7706,10 +7695,10 @@
         <v>84</v>
       </c>
       <c r="J127" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K127" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L127">
         <v>81122101</v>
@@ -7718,10 +7707,10 @@
         <v>52121315</v>
       </c>
       <c r="N127" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="O127" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P127" t="s">
         <v>259</v>
@@ -7730,7 +7719,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" t="str">
         <f>_xlfn.XLOOKUP(I128,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7758,10 +7747,10 @@
         <v>84</v>
       </c>
       <c r="J128" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K128" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L128">
         <v>81122101</v>
@@ -7770,10 +7759,10 @@
         <v>52121402</v>
       </c>
       <c r="N128" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="O128" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P128" t="s">
         <v>259</v>
@@ -7782,7 +7771,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="str">
         <f>_xlfn.XLOOKUP(I129,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7810,10 +7799,10 @@
         <v>84</v>
       </c>
       <c r="J129" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K129" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L129">
         <v>81122101</v>
@@ -7822,19 +7811,19 @@
         <v>52121402</v>
       </c>
       <c r="N129" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="O129" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="P129" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="R129" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="str">
         <f>_xlfn.XLOOKUP(I130,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7862,10 +7851,10 @@
         <v>84</v>
       </c>
       <c r="J130" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K130" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L130">
         <v>81122101</v>
@@ -7880,7 +7869,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="str">
         <f>_xlfn.XLOOKUP(I131,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7908,10 +7897,10 @@
         <v>84</v>
       </c>
       <c r="J131" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K131" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L131">
         <v>81122101</v>
@@ -7923,7 +7912,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="str">
         <f>_xlfn.XLOOKUP(I132,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7951,10 +7940,10 @@
         <v>84</v>
       </c>
       <c r="J132" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K132" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L132">
         <v>81122101</v>
@@ -7966,7 +7955,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="str">
         <f>_xlfn.XLOOKUP(I133,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -7994,10 +7983,10 @@
         <v>84</v>
       </c>
       <c r="J133" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K133" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L133">
         <v>81122101</v>
@@ -8006,19 +7995,19 @@
         <v>52121402</v>
       </c>
       <c r="N133" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="O133" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P133" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="R133" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="str">
         <f>_xlfn.XLOOKUP(I134,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8046,10 +8035,10 @@
         <v>84</v>
       </c>
       <c r="J134" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K134" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L134">
         <v>81122101</v>
@@ -8058,19 +8047,19 @@
         <v>52121402</v>
       </c>
       <c r="N134" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="O134" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P134" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="R134" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="str">
         <f>_xlfn.XLOOKUP(I135,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8100,10 +8089,10 @@
         <v>84</v>
       </c>
       <c r="J135" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K135" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L135">
         <v>90111101</v>
@@ -8112,19 +8101,19 @@
         <v>52121314</v>
       </c>
       <c r="N135" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="O135" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P135" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="R135" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="str">
         <f>_xlfn.XLOOKUP(I136,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8154,10 +8143,10 @@
         <v>84</v>
       </c>
       <c r="J136" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K136" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L136">
         <v>80111101</v>
@@ -8166,16 +8155,19 @@
         <v>61021315</v>
       </c>
       <c r="N136" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="O136" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P136" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+      <c r="R136" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="str">
         <f>_xlfn.XLOOKUP(I137,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8205,10 +8197,10 @@
         <v>84</v>
       </c>
       <c r="J137" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K137" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L137">
         <v>81111101</v>
@@ -8217,16 +8209,19 @@
         <v>52121314</v>
       </c>
       <c r="N137" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="O137" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P137" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+      <c r="R137" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="str">
         <f>_xlfn.XLOOKUP(I138,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8254,10 +8249,10 @@
         <v>84</v>
       </c>
       <c r="J138" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K138" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L138">
         <v>81122101</v>
@@ -8272,7 +8267,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="str">
         <f>_xlfn.XLOOKUP(I139,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8292,7 +8287,7 @@
         <v>268</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G139" s="4"/>
       <c r="H139" s="4"/>
@@ -8300,10 +8295,10 @@
         <v>84</v>
       </c>
       <c r="J139" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K139" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L139">
         <v>81122101</v>
@@ -8312,19 +8307,19 @@
         <v>52121402</v>
       </c>
       <c r="N139" t="s">
+        <v>388</v>
+      </c>
+      <c r="O139" t="s">
+        <v>389</v>
+      </c>
+      <c r="P139" t="s">
         <v>390</v>
       </c>
-      <c r="O139" t="s">
-        <v>391</v>
-      </c>
-      <c r="P139" t="s">
-        <v>392</v>
-      </c>
       <c r="R139" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="str">
         <f>_xlfn.XLOOKUP(I140,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8352,10 +8347,10 @@
         <v>84</v>
       </c>
       <c r="J140" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K140" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L140">
         <v>90122101</v>
@@ -8363,8 +8358,11 @@
       <c r="M140">
         <v>52121402</v>
       </c>
-    </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R140" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="str">
         <f>_xlfn.XLOOKUP(I141,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8384,7 +8382,7 @@
         <v>325</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>221</v>
@@ -8394,10 +8392,10 @@
         <v>84</v>
       </c>
       <c r="J141" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K141" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L141">
         <v>90122101</v>
@@ -8409,7 +8407,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="str">
         <f>_xlfn.XLOOKUP(I142,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8429,7 +8427,7 @@
         <v>325</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G142" s="4" t="s">
         <v>219</v>
@@ -8439,10 +8437,10 @@
         <v>84</v>
       </c>
       <c r="J142" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K142" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L142">
         <v>81122101</v>
@@ -8454,7 +8452,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="str">
         <f>_xlfn.XLOOKUP(I143,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8474,7 +8472,7 @@
         <v>325</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G143" s="4" t="s">
         <v>220</v>
@@ -8484,10 +8482,10 @@
         <v>84</v>
       </c>
       <c r="J143" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K143" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L143">
         <v>80122101</v>
@@ -8499,7 +8497,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:18" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="str">
         <f>_xlfn.XLOOKUP(I144,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8524,10 +8522,10 @@
         <v>84</v>
       </c>
       <c r="J144" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K144" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L144">
         <v>90111101</v>
@@ -8539,7 +8537,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="str">
         <f>_xlfn.XLOOKUP(I145,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8567,10 +8565,10 @@
         <v>84</v>
       </c>
       <c r="J145" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K145" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L145">
         <v>90122101</v>
@@ -8582,7 +8580,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" t="str">
         <f>_xlfn.XLOOKUP(I146,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8602,7 +8600,7 @@
         <v>325</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="G146" s="4"/>
       <c r="H146" s="4"/>
@@ -8610,10 +8608,10 @@
         <v>84</v>
       </c>
       <c r="J146" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K146" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L146">
         <v>90122101</v>
@@ -8621,8 +8619,11 @@
       <c r="M146">
         <v>61071099</v>
       </c>
-    </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R146" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="str">
         <f>_xlfn.XLOOKUP(I147,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8650,10 +8651,10 @@
         <v>84</v>
       </c>
       <c r="J147" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K147" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L147">
         <v>90122101</v>
@@ -8665,7 +8666,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="str">
         <f>_xlfn.XLOOKUP(I148,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8691,10 +8692,10 @@
         <v>84</v>
       </c>
       <c r="J148" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K148" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L148">
         <v>90122101</v>
@@ -8706,7 +8707,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="str">
         <f>_xlfn.XLOOKUP(I149,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8736,10 +8737,10 @@
         <v>84</v>
       </c>
       <c r="J149" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K149" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L149">
         <v>80111101</v>
@@ -8751,7 +8752,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="str">
         <f>_xlfn.XLOOKUP(I150,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8781,10 +8782,10 @@
         <v>84</v>
       </c>
       <c r="J150" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K150" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L150">
         <v>90111101</v>
@@ -8796,7 +8797,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="str">
         <f>_xlfn.XLOOKUP(I151,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8826,10 +8827,10 @@
         <v>84</v>
       </c>
       <c r="J151" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K151" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L151">
         <v>81111101</v>
@@ -8841,7 +8842,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" t="str">
         <f>_xlfn.XLOOKUP(I152,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8869,10 +8870,10 @@
         <v>84</v>
       </c>
       <c r="J152" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K152" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L152">
         <v>81122101</v>
@@ -8884,7 +8885,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="str">
         <f>_xlfn.XLOOKUP(I153,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8912,10 +8913,10 @@
         <v>84</v>
       </c>
       <c r="J153" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K153" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L153">
         <v>81122101</v>
@@ -8927,7 +8928,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" t="str">
         <f>_xlfn.XLOOKUP(I154,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8955,10 +8956,10 @@
         <v>84</v>
       </c>
       <c r="J154" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K154" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L154">
         <v>81122101</v>
@@ -8970,7 +8971,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="str">
         <f>_xlfn.XLOOKUP(I155,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -8998,10 +8999,10 @@
         <v>84</v>
       </c>
       <c r="J155" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K155" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L155">
         <v>81122101</v>
@@ -9009,8 +9010,11 @@
       <c r="M155">
         <v>52111101</v>
       </c>
-    </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R155" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" t="str">
         <f>_xlfn.XLOOKUP(I156,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9038,10 +9042,10 @@
         <v>84</v>
       </c>
       <c r="J156" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K156" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L156">
         <v>81122101</v>
@@ -9053,7 +9057,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" t="str">
         <f>_xlfn.XLOOKUP(I157,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9073,7 +9077,7 @@
         <v>312</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G157" s="4"/>
       <c r="H157" s="4"/>
@@ -9081,10 +9085,10 @@
         <v>84</v>
       </c>
       <c r="J157" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K157" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L157">
         <v>81122101</v>
@@ -9096,7 +9100,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="str">
         <f>_xlfn.XLOOKUP(I158,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9113,7 +9117,7 @@
         <v>HR-27-15</v>
       </c>
       <c r="E158" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F158" s="4" t="s">
         <v>164</v>
@@ -9126,10 +9130,10 @@
         <v>84</v>
       </c>
       <c r="J158" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K158" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L158">
         <v>81122101</v>
@@ -9144,7 +9148,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="str">
         <f>_xlfn.XLOOKUP(I159,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9161,7 +9165,7 @@
         <v>HR-27-16</v>
       </c>
       <c r="E159" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F159" s="4" t="s">
         <v>164</v>
@@ -9174,10 +9178,10 @@
         <v>84</v>
       </c>
       <c r="J159" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K159" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L159">
         <v>90122101</v>
@@ -9192,7 +9196,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="str">
         <f>_xlfn.XLOOKUP(I160,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9222,10 +9226,10 @@
         <v>84</v>
       </c>
       <c r="J160" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K160" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L160">
         <v>81111101</v>
@@ -9237,7 +9241,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="str">
         <f>_xlfn.XLOOKUP(I161,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9267,10 +9271,10 @@
         <v>84</v>
       </c>
       <c r="J161" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K161" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L161">
         <v>80111101</v>
@@ -9282,7 +9286,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" t="str">
         <f>_xlfn.XLOOKUP(I162,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9312,10 +9316,10 @@
         <v>84</v>
       </c>
       <c r="J162" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K162" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L162">
         <v>90111101</v>
@@ -9327,7 +9331,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="str">
         <f>_xlfn.XLOOKUP(I163,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9357,10 +9361,10 @@
         <v>84</v>
       </c>
       <c r="J163" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K163" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L163">
         <v>81111101</v>
@@ -9372,7 +9376,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="str">
         <f>_xlfn.XLOOKUP(I164,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9402,10 +9406,10 @@
         <v>84</v>
       </c>
       <c r="J164" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K164" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L164">
         <v>80111101</v>
@@ -9417,7 +9421,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="str">
         <f>_xlfn.XLOOKUP(I165,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9447,10 +9451,10 @@
         <v>84</v>
       </c>
       <c r="J165" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K165" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L165">
         <v>90111101</v>
@@ -9462,7 +9466,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="str">
         <f>_xlfn.XLOOKUP(I166,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9492,10 +9496,10 @@
         <v>84</v>
       </c>
       <c r="J166" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K166" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L166">
         <v>81111101</v>
@@ -9507,7 +9511,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="str">
         <f>_xlfn.XLOOKUP(I167,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9537,10 +9541,10 @@
         <v>84</v>
       </c>
       <c r="J167" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K167" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L167">
         <v>80111101</v>
@@ -9552,7 +9556,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="str">
         <f>_xlfn.XLOOKUP(I168,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9582,10 +9586,10 @@
         <v>84</v>
       </c>
       <c r="J168" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K168" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L168">
         <v>90111101</v>
@@ -9597,7 +9601,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="str">
         <f>_xlfn.XLOOKUP(I169,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9627,10 +9631,10 @@
         <v>84</v>
       </c>
       <c r="J169" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K169" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L169">
         <v>90111101</v>
@@ -9642,7 +9646,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="str">
         <f>_xlfn.XLOOKUP(I170,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9672,10 +9676,10 @@
         <v>84</v>
       </c>
       <c r="J170" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K170" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L170">
         <v>81111101</v>
@@ -9687,7 +9691,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="str">
         <f>_xlfn.XLOOKUP(I171,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9717,10 +9721,10 @@
         <v>84</v>
       </c>
       <c r="J171" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K171" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L171">
         <v>81111101</v>
@@ -9732,7 +9736,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="str">
         <f>_xlfn.XLOOKUP(I172,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9762,10 +9766,10 @@
         <v>84</v>
       </c>
       <c r="J172" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K172" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L172">
         <v>80111101</v>
@@ -9777,7 +9781,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="str">
         <f>_xlfn.XLOOKUP(I173,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9807,10 +9811,10 @@
         <v>84</v>
       </c>
       <c r="J173" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K173" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L173">
         <v>90111101</v>
@@ -9822,7 +9826,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="str">
         <f>_xlfn.XLOOKUP(I174,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9852,10 +9856,10 @@
         <v>84</v>
       </c>
       <c r="J174" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K174" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L174">
         <v>81111101</v>
@@ -9867,7 +9871,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="str">
         <f>_xlfn.XLOOKUP(I175,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9897,10 +9901,10 @@
         <v>84</v>
       </c>
       <c r="J175" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K175" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L175">
         <v>80111101</v>
@@ -9912,7 +9916,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" t="str">
         <f>_xlfn.XLOOKUP(I176,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9942,10 +9946,10 @@
         <v>84</v>
       </c>
       <c r="J176" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K176" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L176">
         <v>90111101</v>
@@ -9957,7 +9961,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="str">
         <f>_xlfn.XLOOKUP(I177,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -9987,10 +9991,10 @@
         <v>84</v>
       </c>
       <c r="J177" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K177" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L177">
         <v>81111101</v>
@@ -10002,7 +10006,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="str">
         <f>_xlfn.XLOOKUP(I178,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10032,10 +10036,10 @@
         <v>84</v>
       </c>
       <c r="J178" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K178" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L178">
         <v>80111101</v>
@@ -10047,7 +10051,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" t="str">
         <f>_xlfn.XLOOKUP(I179,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10077,10 +10081,10 @@
         <v>84</v>
       </c>
       <c r="J179" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K179" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L179">
         <v>90111101</v>
@@ -10092,7 +10096,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="str">
         <f>_xlfn.XLOOKUP(I180,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10122,10 +10126,10 @@
         <v>84</v>
       </c>
       <c r="J180" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K180" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L180">
         <v>80111101</v>
@@ -10137,7 +10141,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="str">
         <f>_xlfn.XLOOKUP(I181,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10167,10 +10171,10 @@
         <v>84</v>
       </c>
       <c r="J181" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K181" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L181">
         <v>80111101</v>
@@ -10182,7 +10186,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" t="str">
         <f>_xlfn.XLOOKUP(I182,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10212,10 +10216,10 @@
         <v>84</v>
       </c>
       <c r="J182" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K182" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L182">
         <v>90111101</v>
@@ -10227,7 +10231,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="str">
         <f>_xlfn.XLOOKUP(I183,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10257,10 +10261,10 @@
         <v>84</v>
       </c>
       <c r="J183" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K183" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L183">
         <v>81111101</v>
@@ -10272,7 +10276,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="str">
         <f>_xlfn.XLOOKUP(I184,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10302,10 +10306,10 @@
         <v>84</v>
       </c>
       <c r="J184" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K184" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L184">
         <v>81111101</v>
@@ -10317,7 +10321,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="str">
         <f>_xlfn.XLOOKUP(I185,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10345,10 +10349,10 @@
         <v>84</v>
       </c>
       <c r="J185" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K185" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L185">
         <v>90111101</v>
@@ -10360,7 +10364,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" t="str">
         <f>_xlfn.XLOOKUP(I186,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10380,7 +10384,7 @@
         <v>265</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G186" s="4"/>
       <c r="H186" s="4"/>
@@ -10388,10 +10392,10 @@
         <v>84</v>
       </c>
       <c r="J186" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K186" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L186">
         <v>90111101</v>
@@ -10399,8 +10403,11 @@
       <c r="M186">
         <v>52121303</v>
       </c>
-    </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R186" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="str">
         <f>_xlfn.XLOOKUP(I187,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10429,10 +10436,10 @@
         <v>84</v>
       </c>
       <c r="J187" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K187" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L187">
         <v>80111101</v>
@@ -10444,7 +10451,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="str">
         <f>_xlfn.XLOOKUP(I188,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10473,10 +10480,10 @@
         <v>84</v>
       </c>
       <c r="J188" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K188" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L188">
         <v>90111101</v>
@@ -10488,7 +10495,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="str">
         <f>_xlfn.XLOOKUP(I189,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10518,10 +10525,10 @@
         <v>84</v>
       </c>
       <c r="J189" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K189" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L189">
         <v>90111101</v>
@@ -10533,7 +10540,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="str">
         <f>_xlfn.XLOOKUP(I190,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10563,10 +10570,10 @@
         <v>84</v>
       </c>
       <c r="J190" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K190" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L190">
         <v>90111101</v>
@@ -10578,7 +10585,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="str">
         <f>_xlfn.XLOOKUP(I191,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10608,10 +10615,10 @@
         <v>84</v>
       </c>
       <c r="J191" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K191" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L191">
         <v>81111101</v>
@@ -10623,7 +10630,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="str">
         <f>_xlfn.XLOOKUP(I192,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10653,10 +10660,10 @@
         <v>84</v>
       </c>
       <c r="J192" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K192" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L192">
         <v>80111101</v>
@@ -10668,7 +10675,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="str">
         <f>_xlfn.XLOOKUP(I193,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10698,10 +10705,10 @@
         <v>84</v>
       </c>
       <c r="J193" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K193" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L193">
         <v>90111101</v>
@@ -10713,7 +10720,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" t="str">
         <f>_xlfn.XLOOKUP(I194,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10730,7 +10737,7 @@
         <v>HR-27-51</v>
       </c>
       <c r="E194" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F194" s="5" t="s">
         <v>341</v>
@@ -10739,10 +10746,10 @@
         <v>84</v>
       </c>
       <c r="J194" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K194" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L194">
         <v>81111101</v>
@@ -10754,7 +10761,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" t="str">
         <f>_xlfn.XLOOKUP(I195,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10771,7 +10778,7 @@
         <v>HR-27-52</v>
       </c>
       <c r="E195" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>341</v>
@@ -10780,10 +10787,10 @@
         <v>84</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K195" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L195">
         <v>80111101</v>
@@ -10795,7 +10802,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="str">
         <f>_xlfn.XLOOKUP(I196,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10812,7 +10819,7 @@
         <v>HR-27-53</v>
       </c>
       <c r="E196" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F196" s="5" t="s">
         <v>341</v>
@@ -10821,10 +10828,10 @@
         <v>84</v>
       </c>
       <c r="J196" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K196" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L196">
         <v>90111101</v>
@@ -10836,7 +10843,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="str">
         <f>_xlfn.XLOOKUP(I197,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10853,10 +10860,10 @@
         <v>HR-27-54</v>
       </c>
       <c r="E197" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F197" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G197" s="5" t="s">
         <v>219</v>
@@ -10866,10 +10873,10 @@
         <v>84</v>
       </c>
       <c r="J197" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K197" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L197">
         <v>81111101</v>
@@ -10881,7 +10888,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="str">
         <f>_xlfn.XLOOKUP(I198,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10898,10 +10905,10 @@
         <v>HR-27-55</v>
       </c>
       <c r="E198" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F198" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G198" s="5" t="s">
         <v>220</v>
@@ -10911,10 +10918,10 @@
         <v>84</v>
       </c>
       <c r="J198" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K198" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L198">
         <v>80111101</v>
@@ -10926,7 +10933,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="str">
         <f>_xlfn.XLOOKUP(I199,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10943,10 +10950,10 @@
         <v>HR-27-56</v>
       </c>
       <c r="E199" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F199" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G199" s="5" t="s">
         <v>221</v>
@@ -10956,10 +10963,10 @@
         <v>84</v>
       </c>
       <c r="J199" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K199" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L199">
         <v>90111101</v>
@@ -10971,7 +10978,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="str">
         <f>_xlfn.XLOOKUP(I200,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -10988,10 +10995,10 @@
         <v>HR-27-57</v>
       </c>
       <c r="E200" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F200" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G200" s="5" t="s">
         <v>219</v>
@@ -11001,10 +11008,10 @@
         <v>84</v>
       </c>
       <c r="J200" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K200" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L200">
         <v>81111101</v>
@@ -11016,7 +11023,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="str">
         <f>_xlfn.XLOOKUP(I201,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11033,10 +11040,10 @@
         <v>HR-27-58</v>
       </c>
       <c r="E201" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F201" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G201" s="5" t="s">
         <v>220</v>
@@ -11046,10 +11053,10 @@
         <v>84</v>
       </c>
       <c r="J201" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K201" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L201">
         <v>80111101</v>
@@ -11061,7 +11068,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="str">
         <f>_xlfn.XLOOKUP(I202,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11078,10 +11085,10 @@
         <v>HR-27-59</v>
       </c>
       <c r="E202" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F202" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G202" s="5" t="s">
         <v>221</v>
@@ -11091,10 +11098,10 @@
         <v>84</v>
       </c>
       <c r="J202" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K202" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L202">
         <v>90111101</v>
@@ -11106,7 +11113,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="str">
         <f>_xlfn.XLOOKUP(I203,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11123,10 +11130,10 @@
         <v>HR-27-60</v>
       </c>
       <c r="E203" t="s">
+        <v>357</v>
+      </c>
+      <c r="F203" t="s">
         <v>358</v>
-      </c>
-      <c r="F203" t="s">
-        <v>359</v>
       </c>
       <c r="G203" s="5" t="s">
         <v>219</v>
@@ -11136,10 +11143,10 @@
         <v>84</v>
       </c>
       <c r="J203" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K203" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L203">
         <v>81111101</v>
@@ -11151,7 +11158,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="str">
         <f>_xlfn.XLOOKUP(I204,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11168,10 +11175,10 @@
         <v>HR-27-61</v>
       </c>
       <c r="E204" t="s">
+        <v>357</v>
+      </c>
+      <c r="F204" t="s">
         <v>358</v>
-      </c>
-      <c r="F204" t="s">
-        <v>359</v>
       </c>
       <c r="G204" s="5" t="s">
         <v>220</v>
@@ -11181,10 +11188,10 @@
         <v>84</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K204" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L204">
         <v>80111101</v>
@@ -11196,7 +11203,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="str">
         <f>_xlfn.XLOOKUP(I205,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11213,10 +11220,10 @@
         <v>HR-27-62</v>
       </c>
       <c r="E205" t="s">
+        <v>357</v>
+      </c>
+      <c r="F205" t="s">
         <v>358</v>
-      </c>
-      <c r="F205" t="s">
-        <v>359</v>
       </c>
       <c r="G205" s="5" t="s">
         <v>221</v>
@@ -11226,10 +11233,10 @@
         <v>84</v>
       </c>
       <c r="J205" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K205" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L205">
         <v>90111101</v>
@@ -11241,7 +11248,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="str">
         <f>_xlfn.XLOOKUP(I206,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11258,7 +11265,7 @@
         <v>HR-27-63</v>
       </c>
       <c r="E206" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F206" s="5" t="s">
         <v>342</v>
@@ -11267,10 +11274,10 @@
         <v>84</v>
       </c>
       <c r="J206" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K206" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L206">
         <v>81111101</v>
@@ -11282,7 +11289,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="str">
         <f>_xlfn.XLOOKUP(I207,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11299,7 +11306,7 @@
         <v>HR-27-64</v>
       </c>
       <c r="E207" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F207" s="5" t="s">
         <v>342</v>
@@ -11308,10 +11315,10 @@
         <v>84</v>
       </c>
       <c r="J207" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K207" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L207">
         <v>80111101</v>
@@ -11323,7 +11330,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="str">
         <f>_xlfn.XLOOKUP(I208,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11340,7 +11347,7 @@
         <v>HR-27-65</v>
       </c>
       <c r="E208" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F208" s="5" t="s">
         <v>342</v>
@@ -11349,10 +11356,10 @@
         <v>84</v>
       </c>
       <c r="J208" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K208" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L208">
         <v>90111101</v>
@@ -11364,7 +11371,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="str">
         <f>_xlfn.XLOOKUP(I209,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11381,7 +11388,7 @@
         <v>HR-27-66</v>
       </c>
       <c r="E209" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F209" s="5" t="s">
         <v>343</v>
@@ -11390,10 +11397,10 @@
         <v>84</v>
       </c>
       <c r="J209" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K209" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L209">
         <v>81111101</v>
@@ -11405,7 +11412,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="str">
         <f>_xlfn.XLOOKUP(I210,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11422,7 +11429,7 @@
         <v>HR-27-67</v>
       </c>
       <c r="E210" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F210" s="5" t="s">
         <v>344</v>
@@ -11434,10 +11441,10 @@
         <v>84</v>
       </c>
       <c r="J210" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K210" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L210">
         <v>80111101</v>
@@ -11449,7 +11456,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="str">
         <f>_xlfn.XLOOKUP(I211,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11466,7 +11473,7 @@
         <v>HR-27-68</v>
       </c>
       <c r="E211" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F211" s="5" t="s">
         <v>344</v>
@@ -11478,10 +11485,10 @@
         <v>84</v>
       </c>
       <c r="J211" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K211" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L211">
         <v>90111101</v>
@@ -11493,7 +11500,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:18" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="str">
         <f>_xlfn.XLOOKUP(I212,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11510,7 +11517,7 @@
         <v>HR-27-69</v>
       </c>
       <c r="E212" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F212" s="5" t="s">
         <v>346</v>
@@ -11522,10 +11529,10 @@
         <v>84</v>
       </c>
       <c r="J212" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K212" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L212">
         <v>80111101</v>
@@ -11537,7 +11544,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:18" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="str">
         <f>_xlfn.XLOOKUP(I213,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11554,7 +11561,7 @@
         <v>HR-27-70</v>
       </c>
       <c r="E213" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F213" s="5" t="s">
         <v>346</v>
@@ -11566,10 +11573,10 @@
         <v>84</v>
       </c>
       <c r="J213" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K213" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L213">
         <v>90111101</v>
@@ -11581,7 +11588,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" t="str">
         <f>_xlfn.XLOOKUP(I214,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11601,16 +11608,16 @@
         <v>267</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I214" t="s">
         <v>84</v>
       </c>
       <c r="J214" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K214" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L214">
         <v>81122101</v>
@@ -11619,7 +11626,7 @@
         <v>52952101</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="str">
         <f>_xlfn.XLOOKUP(I215,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11647,10 +11654,10 @@
         <v>84</v>
       </c>
       <c r="J215" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K215" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L215">
         <v>81122101</v>
@@ -11659,7 +11666,7 @@
         <v>52952101</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="str">
         <f>_xlfn.XLOOKUP(I216,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11687,10 +11694,10 @@
         <v>84</v>
       </c>
       <c r="J216" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K216" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L216">
         <v>81122101</v>
@@ -11699,7 +11706,7 @@
         <v>52952101</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="str">
         <f>_xlfn.XLOOKUP(I217,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11727,10 +11734,10 @@
         <v>84</v>
       </c>
       <c r="J217" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K217" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L217">
         <v>81122101</v>
@@ -11739,7 +11746,7 @@
         <v>52952101</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:18" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="str">
         <f>_xlfn.XLOOKUP(I218,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11759,16 +11766,16 @@
         <v>267</v>
       </c>
       <c r="F218" s="5" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I218" t="s">
         <v>84</v>
       </c>
       <c r="J218" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K218" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L218">
         <v>81122101</v>
@@ -11777,7 +11784,7 @@
         <v>52952101</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="str">
         <f>_xlfn.XLOOKUP(I219,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11805,10 +11812,10 @@
         <v>84</v>
       </c>
       <c r="J219" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K219" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L219">
         <v>81122101</v>
@@ -11817,7 +11824,7 @@
         <v>52952101</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="str">
         <f>_xlfn.XLOOKUP(I220,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11845,10 +11852,10 @@
         <v>84</v>
       </c>
       <c r="J220" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K220" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L220">
         <v>81122101</v>
@@ -11857,7 +11864,7 @@
         <v>52952101</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="str">
         <f>_xlfn.XLOOKUP(I221,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11885,10 +11892,10 @@
         <v>84</v>
       </c>
       <c r="J221" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K221" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L221">
         <v>81122101</v>
@@ -11897,7 +11904,7 @@
         <v>52952101</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:18" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="str">
         <f>_xlfn.XLOOKUP(I222,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11923,10 +11930,10 @@
         <v>84</v>
       </c>
       <c r="J222" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K222" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L222">
         <v>81134102</v>
@@ -11935,7 +11942,7 @@
         <v>52952101</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="str">
         <f>_xlfn.XLOOKUP(I223,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11963,10 +11970,10 @@
         <v>84</v>
       </c>
       <c r="J223" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K223" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L223">
         <v>81122101</v>
@@ -11975,7 +11982,7 @@
         <v>52952101</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="str">
         <f>_xlfn.XLOOKUP(I224,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -11995,7 +12002,7 @@
         <v>267</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G224" s="4"/>
       <c r="H224" s="4"/>
@@ -12003,10 +12010,10 @@
         <v>84</v>
       </c>
       <c r="J224" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K224" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L224">
         <v>81122101</v>
@@ -12015,7 +12022,7 @@
         <v>52952101</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="str">
         <f>_xlfn.XLOOKUP(I225,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12043,10 +12050,10 @@
         <v>84</v>
       </c>
       <c r="J225" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K225" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L225">
         <v>81122101</v>
@@ -12058,7 +12065,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" t="str">
         <f>_xlfn.XLOOKUP(I226,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12086,10 +12093,10 @@
         <v>84</v>
       </c>
       <c r="J226" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K226" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L226">
         <v>81122101</v>
@@ -12101,7 +12108,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="str">
         <f>_xlfn.XLOOKUP(I227,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12129,10 +12136,10 @@
         <v>84</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K227" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L227">
         <v>81122101</v>
@@ -12144,7 +12151,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="str">
         <f>_xlfn.XLOOKUP(I228,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12172,10 +12179,10 @@
         <v>84</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K228" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L228">
         <v>81122101</v>
@@ -12187,7 +12194,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="str">
         <f>_xlfn.XLOOKUP(I229,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12215,10 +12222,10 @@
         <v>84</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K229" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L229">
         <v>81122101</v>
@@ -12230,7 +12237,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="str">
         <f>_xlfn.XLOOKUP(I230,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12258,10 +12265,10 @@
         <v>84</v>
       </c>
       <c r="J230" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K230" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L230">
         <v>81122101</v>
@@ -12273,7 +12280,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="str">
         <f>_xlfn.XLOOKUP(I231,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12301,10 +12308,10 @@
         <v>84</v>
       </c>
       <c r="J231" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K231" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L231">
         <v>81122101</v>
@@ -12316,7 +12323,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="str">
         <f>_xlfn.XLOOKUP(I232,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12344,10 +12351,10 @@
         <v>84</v>
       </c>
       <c r="J232" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K232" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L232">
         <v>81122101</v>
@@ -12356,19 +12363,19 @@
         <v>52121315</v>
       </c>
       <c r="N232" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="O232" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P232" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="R232" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="str">
         <f>_xlfn.XLOOKUP(I233,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12396,10 +12403,10 @@
         <v>84</v>
       </c>
       <c r="J233" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K233" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L233">
         <v>81122101</v>
@@ -12411,7 +12418,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="str">
         <f>_xlfn.XLOOKUP(I234,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12439,10 +12446,10 @@
         <v>84</v>
       </c>
       <c r="J234" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K234" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L234">
         <v>81122101</v>
@@ -12454,7 +12461,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="str">
         <f>_xlfn.XLOOKUP(I235,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12482,10 +12489,10 @@
         <v>84</v>
       </c>
       <c r="J235" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K235" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L235">
         <v>81122101</v>
@@ -12497,7 +12504,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="str">
         <f>_xlfn.XLOOKUP(I236,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12525,10 +12532,10 @@
         <v>84</v>
       </c>
       <c r="J236" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K236" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L236">
         <v>81122101</v>
@@ -12540,7 +12547,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="str">
         <f>_xlfn.XLOOKUP(I237,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12568,10 +12575,10 @@
         <v>84</v>
       </c>
       <c r="J237" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K237" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L237">
         <v>81122101</v>
@@ -12583,7 +12590,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="str">
         <f>_xlfn.XLOOKUP(I238,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12603,7 +12610,7 @@
         <v>131</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G238" s="4"/>
       <c r="H238" s="4"/>
@@ -12611,10 +12618,10 @@
         <v>84</v>
       </c>
       <c r="J238" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K238" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L238">
         <v>81122101</v>
@@ -12626,7 +12633,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="str">
         <f>_xlfn.XLOOKUP(I239,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12654,10 +12661,10 @@
         <v>84</v>
       </c>
       <c r="J239" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K239" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L239">
         <v>81122101</v>
@@ -12669,7 +12676,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="str">
         <f>_xlfn.XLOOKUP(I240,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12697,10 +12704,10 @@
         <v>84</v>
       </c>
       <c r="J240" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K240" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L240">
         <v>81122101</v>
@@ -12712,7 +12719,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="str">
         <f>_xlfn.XLOOKUP(I241,Lookup!A:A,Lookup!B:B)</f>
         <v>HR</v>
@@ -12740,10 +12747,10 @@
         <v>84</v>
       </c>
       <c r="J241" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K241" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L241">
         <v>81122101</v>
@@ -12752,7 +12759,7 @@
         <v>52121502</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="str">
         <f>_xlfn.XLOOKUP(I242,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -12771,16 +12778,16 @@
         <v>325</v>
       </c>
       <c r="F242" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I242" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J242" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="K242" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L242">
         <v>81124101</v>
@@ -12789,7 +12796,7 @@
         <v>52071104</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="str">
         <f>_xlfn.XLOOKUP(I243,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -12809,16 +12816,16 @@
         <v>325</v>
       </c>
       <c r="F243" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I243" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J243" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="K243" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L243">
         <v>81124101</v>
@@ -12827,7 +12834,7 @@
         <v>52071104</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="str">
         <f>_xlfn.XLOOKUP(I244,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -12847,16 +12854,16 @@
         <v>325</v>
       </c>
       <c r="F244" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I244" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J244" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="K244" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L244">
         <v>81124101</v>
@@ -12865,7 +12872,7 @@
         <v>52071104</v>
       </c>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="str">
         <f>_xlfn.XLOOKUP(I245,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -12885,16 +12892,16 @@
         <v>325</v>
       </c>
       <c r="F245" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I245" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J245" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="K245" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L245">
         <v>81124101</v>
@@ -12903,7 +12910,7 @@
         <v>52071104</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="str">
         <f>_xlfn.XLOOKUP(I246,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -12923,16 +12930,16 @@
         <v>325</v>
       </c>
       <c r="F246" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="I246" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J246" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="K246" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L246">
         <v>81124101</v>
@@ -12941,7 +12948,7 @@
         <v>52071104</v>
       </c>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="str">
         <f>_xlfn.XLOOKUP(I247,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -12961,16 +12968,16 @@
         <v>325</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I247" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J247" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="K247" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L247">
         <v>81124101</v>
@@ -12979,7 +12986,7 @@
         <v>52071104</v>
       </c>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="str">
         <f>_xlfn.XLOOKUP(I248,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13002,13 +13009,13 @@
         <v>295</v>
       </c>
       <c r="I248" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J248" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K248" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L248">
         <v>80124101</v>
@@ -13020,7 +13027,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="str">
         <f>_xlfn.XLOOKUP(I249,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13043,13 +13050,13 @@
         <v>297</v>
       </c>
       <c r="I249" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J249" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K249" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L249">
         <v>80124101</v>
@@ -13061,7 +13068,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="str">
         <f>_xlfn.XLOOKUP(I250,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13084,13 +13091,13 @@
         <v>292</v>
       </c>
       <c r="I250" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J250" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K250" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L250">
         <v>80124101</v>
@@ -13102,7 +13109,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="str">
         <f>_xlfn.XLOOKUP(I251,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13125,13 +13132,13 @@
         <v>296</v>
       </c>
       <c r="I251" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J251" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K251" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L251">
         <v>80124101</v>
@@ -13143,7 +13150,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="str">
         <f>_xlfn.XLOOKUP(I252,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13166,13 +13173,13 @@
         <v>293</v>
       </c>
       <c r="I252" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J252" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K252" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L252">
         <v>80124101</v>
@@ -13184,7 +13191,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="str">
         <f>_xlfn.XLOOKUP(I253,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13207,13 +13214,13 @@
         <v>294</v>
       </c>
       <c r="I253" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J253" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K253" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L253">
         <v>80124101</v>
@@ -13225,7 +13232,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" t="str">
         <f>_xlfn.XLOOKUP(I254,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13245,16 +13252,16 @@
         <v>291</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="I254" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J254" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K254" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L254">
         <v>80124101</v>
@@ -13266,7 +13273,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="str">
         <f>_xlfn.XLOOKUP(I255,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13292,13 +13299,13 @@
         <v>206</v>
       </c>
       <c r="I255" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J255" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="K255" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L255">
         <v>81124101</v>
@@ -13307,7 +13314,7 @@
         <v>52952103</v>
       </c>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="str">
         <f>_xlfn.XLOOKUP(I256,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13324,7 +13331,7 @@
         <v>IT-27-15</v>
       </c>
       <c r="E256" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F256" s="5" t="s">
         <v>48</v>
@@ -13333,13 +13340,13 @@
         <v>185</v>
       </c>
       <c r="I256" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J256" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K256" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L256">
         <v>81124101</v>
@@ -13351,7 +13358,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="str">
         <f>_xlfn.XLOOKUP(I257,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13368,7 +13375,7 @@
         <v>IT-27-16</v>
       </c>
       <c r="E257" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F257" s="5" t="s">
         <v>47</v>
@@ -13377,13 +13384,13 @@
         <v>201</v>
       </c>
       <c r="I257" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J257" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K257" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L257">
         <v>81124101</v>
@@ -13395,7 +13402,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="str">
         <f>_xlfn.XLOOKUP(I258,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13412,20 +13419,20 @@
         <v>IT-27-17</v>
       </c>
       <c r="E258" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F258" s="5" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="H258"/>
       <c r="I258" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J258" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K258" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L258">
         <v>81124101</v>
@@ -13433,8 +13440,11 @@
       <c r="M258">
         <v>52061109</v>
       </c>
-    </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R258" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="259" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="str">
         <f>_xlfn.XLOOKUP(I259,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13460,13 +13470,13 @@
         <v>198</v>
       </c>
       <c r="I259" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J259" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K259" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L259">
         <v>80124101</v>
@@ -13478,7 +13488,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="str">
         <f>_xlfn.XLOOKUP(I260,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13504,13 +13514,13 @@
         <v>173</v>
       </c>
       <c r="I260" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J260" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K260" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L260">
         <v>81124101</v>
@@ -13522,7 +13532,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="str">
         <f>_xlfn.XLOOKUP(I261,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13548,13 +13558,13 @@
         <v>190</v>
       </c>
       <c r="I261" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J261" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K261" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L261">
         <v>80124101</v>
@@ -13566,7 +13576,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="str">
         <f>_xlfn.XLOOKUP(I262,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13592,13 +13602,13 @@
         <v>202</v>
       </c>
       <c r="I262" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J262" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K262" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L262">
         <v>80124101</v>
@@ -13610,7 +13620,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="str">
         <f>_xlfn.XLOOKUP(I263,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13636,13 +13646,13 @@
         <v>205</v>
       </c>
       <c r="I263" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J263" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K263" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L263">
         <v>80124101</v>
@@ -13654,7 +13664,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="264" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="str">
         <f>_xlfn.XLOOKUP(I264,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13671,22 +13681,22 @@
         <v>IT-27-23</v>
       </c>
       <c r="E264" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F264" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G264" s="5" t="s">
         <v>219</v>
       </c>
       <c r="I264" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J264" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K264" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L264">
         <v>81124101</v>
@@ -13695,7 +13705,7 @@
         <v>52061109</v>
       </c>
     </row>
-    <row r="265" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="str">
         <f>_xlfn.XLOOKUP(I265,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13712,22 +13722,22 @@
         <v>IT-27-24</v>
       </c>
       <c r="E265" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F265" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G265" s="5" t="s">
         <v>220</v>
       </c>
       <c r="I265" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J265" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K265" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L265">
         <v>80124101</v>
@@ -13736,7 +13746,7 @@
         <v>61061105</v>
       </c>
     </row>
-    <row r="266" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="str">
         <f>_xlfn.XLOOKUP(I266,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13753,22 +13763,22 @@
         <v>IT-27-25</v>
       </c>
       <c r="E266" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F266" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G266" s="5" t="s">
         <v>221</v>
       </c>
       <c r="I266" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J266" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K266" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L266">
         <v>90124101</v>
@@ -13777,7 +13787,7 @@
         <v>61061105</v>
       </c>
     </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="str">
         <f>_xlfn.XLOOKUP(I267,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13794,22 +13804,22 @@
         <v>IT-27-26</v>
       </c>
       <c r="E267" t="s">
+        <v>416</v>
+      </c>
+      <c r="F267" s="5" t="s">
         <v>418</v>
-      </c>
-      <c r="F267" s="5" t="s">
-        <v>420</v>
       </c>
       <c r="G267" s="5" t="s">
         <v>219</v>
       </c>
       <c r="I267" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J267" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K267" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L267">
         <v>81124101</v>
@@ -13818,7 +13828,7 @@
         <v>52061109</v>
       </c>
     </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" t="str">
         <f>_xlfn.XLOOKUP(I268,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13835,22 +13845,22 @@
         <v>IT-27-27</v>
       </c>
       <c r="E268" t="s">
+        <v>416</v>
+      </c>
+      <c r="F268" s="5" t="s">
         <v>418</v>
-      </c>
-      <c r="F268" s="5" t="s">
-        <v>420</v>
       </c>
       <c r="G268" s="5" t="s">
         <v>220</v>
       </c>
       <c r="I268" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J268" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K268" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L268">
         <v>80124101</v>
@@ -13859,7 +13869,7 @@
         <v>61061105</v>
       </c>
     </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="str">
         <f>_xlfn.XLOOKUP(I269,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13876,22 +13886,22 @@
         <v>IT-27-28</v>
       </c>
       <c r="E269" t="s">
+        <v>416</v>
+      </c>
+      <c r="F269" s="5" t="s">
         <v>418</v>
-      </c>
-      <c r="F269" s="5" t="s">
-        <v>420</v>
       </c>
       <c r="G269" s="5" t="s">
         <v>221</v>
       </c>
       <c r="I269" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J269" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K269" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L269">
         <v>90124101</v>
@@ -13900,7 +13910,7 @@
         <v>61061105</v>
       </c>
     </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" t="str">
         <f>_xlfn.XLOOKUP(I270,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13926,13 +13936,13 @@
         <v>168</v>
       </c>
       <c r="I270" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J270" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K270" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L270">
         <v>81124101</v>
@@ -13944,7 +13954,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="str">
         <f>_xlfn.XLOOKUP(I271,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -13964,19 +13974,19 @@
         <v>208</v>
       </c>
       <c r="F271" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H271" t="s">
         <v>178</v>
       </c>
       <c r="I271" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J271" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K271" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L271">
         <v>80124101</v>
@@ -13988,7 +13998,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="str">
         <f>_xlfn.XLOOKUP(I272,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14014,13 +14024,13 @@
         <v>182</v>
       </c>
       <c r="I272" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J272" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K272" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L272">
         <v>80124101</v>
@@ -14032,7 +14042,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="273" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:18" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" t="str">
         <f>_xlfn.XLOOKUP(I273,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14058,13 +14068,13 @@
         <v>187</v>
       </c>
       <c r="I273" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J273" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K273" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L273">
         <v>80124101</v>
@@ -14076,7 +14086,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="274" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:18" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" t="str">
         <f>_xlfn.XLOOKUP(I274,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14102,13 +14112,13 @@
         <v>188</v>
       </c>
       <c r="I274" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J274" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K274" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L274">
         <v>80124101</v>
@@ -14120,7 +14130,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="str">
         <f>_xlfn.XLOOKUP(I275,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14146,13 +14156,13 @@
         <v>189</v>
       </c>
       <c r="I275" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J275" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K275" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L275">
         <v>80124101</v>
@@ -14164,7 +14174,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="str">
         <f>_xlfn.XLOOKUP(I276,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14190,13 +14200,13 @@
         <v>197</v>
       </c>
       <c r="I276" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J276" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K276" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L276">
         <v>80124101</v>
@@ -14208,7 +14218,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="str">
         <f>_xlfn.XLOOKUP(I277,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14228,17 +14238,17 @@
         <v>208</v>
       </c>
       <c r="F277" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H277"/>
       <c r="I277" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J277" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K277" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L277">
         <v>80124101</v>
@@ -14250,7 +14260,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="str">
         <f>_xlfn.XLOOKUP(I278,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14276,13 +14286,13 @@
         <v>200</v>
       </c>
       <c r="I278" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J278" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K278" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L278">
         <v>81124101</v>
@@ -14294,7 +14304,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="str">
         <f>_xlfn.XLOOKUP(I279,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14320,13 +14330,13 @@
         <v>204</v>
       </c>
       <c r="I279" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J279" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K279" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L279">
         <v>81124101</v>
@@ -14338,7 +14348,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="str">
         <f>_xlfn.XLOOKUP(I280,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14358,17 +14368,17 @@
         <v>208</v>
       </c>
       <c r="F280" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H280"/>
       <c r="I280" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J280" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K280" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L280">
         <v>81124101</v>
@@ -14376,8 +14386,11 @@
       <c r="M280">
         <v>52952103</v>
       </c>
-    </row>
-    <row r="281" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R280" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="281" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="str">
         <f>_xlfn.XLOOKUP(I281,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14403,13 +14416,13 @@
         <v>176</v>
       </c>
       <c r="I281" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J281" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K281" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L281">
         <v>80124101</v>
@@ -14421,7 +14434,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="str">
         <f>_xlfn.XLOOKUP(I282,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14447,13 +14460,13 @@
         <v>167</v>
       </c>
       <c r="I282" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J282" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K282" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L282">
         <v>81124101</v>
@@ -14465,7 +14478,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="str">
         <f>_xlfn.XLOOKUP(I283,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14491,13 +14504,13 @@
         <v>169</v>
       </c>
       <c r="I283" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J283" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K283" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L283">
         <v>80124101</v>
@@ -14506,7 +14519,7 @@
         <v>61711102</v>
       </c>
     </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" t="str">
         <f>_xlfn.XLOOKUP(I284,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14532,13 +14545,13 @@
         <v>170</v>
       </c>
       <c r="I284" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J284" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K284" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L284">
         <v>80124101</v>
@@ -14547,7 +14560,7 @@
         <v>61711102</v>
       </c>
     </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="str">
         <f>_xlfn.XLOOKUP(I285,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14573,13 +14586,13 @@
         <v>171</v>
       </c>
       <c r="I285" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J285" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K285" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L285">
         <v>80124101</v>
@@ -14588,7 +14601,7 @@
         <v>61711102</v>
       </c>
     </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="str">
         <f>_xlfn.XLOOKUP(I286,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14608,17 +14621,17 @@
         <v>211</v>
       </c>
       <c r="F286" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H286"/>
       <c r="I286" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J286" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K286" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L286">
         <v>80124101</v>
@@ -14627,7 +14640,7 @@
         <v>61711102</v>
       </c>
     </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="str">
         <f>_xlfn.XLOOKUP(I287,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14647,17 +14660,17 @@
         <v>211</v>
       </c>
       <c r="F287" s="5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H287"/>
       <c r="I287" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J287" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K287" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L287">
         <v>81124101</v>
@@ -14666,7 +14679,7 @@
         <v>52952103</v>
       </c>
     </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="str">
         <f>_xlfn.XLOOKUP(I288,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14692,13 +14705,13 @@
         <v>174</v>
       </c>
       <c r="I288" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J288" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K288" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L288">
         <v>81124101</v>
@@ -14707,7 +14720,7 @@
         <v>52952103</v>
       </c>
     </row>
-    <row r="289" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="str">
         <f>_xlfn.XLOOKUP(I289,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14727,17 +14740,17 @@
         <v>211</v>
       </c>
       <c r="F289" s="5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H289"/>
       <c r="I289" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J289" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K289" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L289">
         <v>81124101</v>
@@ -14746,7 +14759,7 @@
         <v>52952103</v>
       </c>
     </row>
-    <row r="290" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" t="str">
         <f>_xlfn.XLOOKUP(I290,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14772,13 +14785,13 @@
         <v>177</v>
       </c>
       <c r="I290" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J290" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K290" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L290">
         <v>80124101</v>
@@ -14787,7 +14800,7 @@
         <v>61711102</v>
       </c>
     </row>
-    <row r="291" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" t="str">
         <f>_xlfn.XLOOKUP(I291,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14811,13 +14824,13 @@
       </c>
       <c r="H291"/>
       <c r="I291" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J291" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K291" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L291">
         <v>81124101</v>
@@ -14826,7 +14839,7 @@
         <v>52952103</v>
       </c>
     </row>
-    <row r="292" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" t="str">
         <f>_xlfn.XLOOKUP(I292,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14852,13 +14865,13 @@
         <v>181</v>
       </c>
       <c r="I292" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J292" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K292" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L292">
         <v>80124101</v>
@@ -14870,7 +14883,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="293" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" t="str">
         <f>_xlfn.XLOOKUP(I293,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14896,13 +14909,13 @@
         <v>183</v>
       </c>
       <c r="I293" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J293" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K293" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L293">
         <v>80124101</v>
@@ -14914,7 +14927,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" t="str">
         <f>_xlfn.XLOOKUP(I294,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14940,13 +14953,13 @@
         <v>184</v>
       </c>
       <c r="I294" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J294" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K294" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L294">
         <v>81124101</v>
@@ -14955,7 +14968,7 @@
         <v>52952103</v>
       </c>
     </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" t="str">
         <f>_xlfn.XLOOKUP(I295,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -14981,13 +14994,13 @@
         <v>186</v>
       </c>
       <c r="I295" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J295" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K295" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L295">
         <v>80124101</v>
@@ -14999,7 +15012,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="296" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:18" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" t="str">
         <f>_xlfn.XLOOKUP(I296,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -15025,13 +15038,13 @@
         <v>191</v>
       </c>
       <c r="I296" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J296" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K296" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L296">
         <v>80124101</v>
@@ -15040,7 +15053,7 @@
         <v>61711102</v>
       </c>
     </row>
-    <row r="297" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" t="str">
         <f>_xlfn.XLOOKUP(I297,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -15060,17 +15073,17 @@
         <v>211</v>
       </c>
       <c r="F297" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H297"/>
       <c r="I297" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J297" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K297" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L297">
         <v>81124101</v>
@@ -15079,7 +15092,7 @@
         <v>52952103</v>
       </c>
     </row>
-    <row r="298" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" t="str">
         <f>_xlfn.XLOOKUP(I298,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -15099,19 +15112,19 @@
         <v>211</v>
       </c>
       <c r="F298" s="5" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H298" t="s">
         <v>192</v>
       </c>
       <c r="I298" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J298" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K298" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L298">
         <v>81124101</v>
@@ -15123,7 +15136,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="299" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" t="str">
         <f>_xlfn.XLOOKUP(I299,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -15149,13 +15162,13 @@
         <v>193</v>
       </c>
       <c r="I299" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J299" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K299" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L299">
         <v>80124101</v>
@@ -15167,7 +15180,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="300" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:18" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" t="str">
         <f>_xlfn.XLOOKUP(I300,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -15193,13 +15206,13 @@
         <v>194</v>
       </c>
       <c r="I300" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J300" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K300" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L300">
         <v>80124101</v>
@@ -15211,7 +15224,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="301" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" t="str">
         <f>_xlfn.XLOOKUP(I301,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -15237,13 +15250,13 @@
         <v>195</v>
       </c>
       <c r="I301" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J301" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K301" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L301">
         <v>80124101</v>
@@ -15252,7 +15265,7 @@
         <v>61711102</v>
       </c>
     </row>
-    <row r="302" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" t="str">
         <f>_xlfn.XLOOKUP(I302,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -15278,13 +15291,13 @@
         <v>196</v>
       </c>
       <c r="I302" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J302" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K302" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L302">
         <v>80124101</v>
@@ -15293,7 +15306,7 @@
         <v>61711102</v>
       </c>
     </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" t="str">
         <f>_xlfn.XLOOKUP(I303,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -15317,13 +15330,13 @@
       </c>
       <c r="H303"/>
       <c r="I303" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J303" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K303" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L303">
         <v>80124101</v>
@@ -15335,7 +15348,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="304" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" t="str">
         <f>_xlfn.XLOOKUP(I304,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -15355,17 +15368,17 @@
         <v>211</v>
       </c>
       <c r="F304" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H304"/>
       <c r="I304" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J304" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K304" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L304">
         <v>81124101</v>
@@ -15374,7 +15387,7 @@
         <v>52952103</v>
       </c>
     </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" t="str">
         <f>_xlfn.XLOOKUP(I305,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -15400,13 +15413,13 @@
         <v>199</v>
       </c>
       <c r="I305" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J305" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K305" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L305">
         <v>80124101</v>
@@ -15415,7 +15428,7 @@
         <v>61711102</v>
       </c>
     </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" t="str">
         <f>_xlfn.XLOOKUP(I306,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -15441,13 +15454,13 @@
         <v>203</v>
       </c>
       <c r="I306" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J306" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K306" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L306">
         <v>81124101</v>
@@ -15456,7 +15469,7 @@
         <v>52952103</v>
       </c>
     </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" t="str">
         <f>_xlfn.XLOOKUP(I307,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -15480,13 +15493,13 @@
       </c>
       <c r="H307"/>
       <c r="I307" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J307" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K307" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L307">
         <v>80124101</v>
@@ -15495,7 +15508,7 @@
         <v>61711102</v>
       </c>
     </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" t="str">
         <f>_xlfn.XLOOKUP(I308,Lookup!A:A,Lookup!B:B)</f>
         <v>IT</v>
@@ -15521,13 +15534,13 @@
         <v>180</v>
       </c>
       <c r="I308" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J308" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K308" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L308">
         <v>81124101</v>
@@ -15539,7 +15552,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" t="str">
         <f>_xlfn.XLOOKUP(I309,Lookup!A:A,Lookup!B:B)</f>
         <v>LG</v>
@@ -15559,16 +15572,16 @@
         <v>264</v>
       </c>
       <c r="F309" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I309" s="5" t="s">
         <v>323</v>
       </c>
       <c r="J309" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K309" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L309">
         <v>90122101</v>
@@ -15577,7 +15590,7 @@
         <v>61711101</v>
       </c>
     </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" t="str">
         <f>_xlfn.XLOOKUP(I310,Lookup!A:A,Lookup!B:B)</f>
         <v>LG</v>
@@ -15605,10 +15618,10 @@
         <v>323</v>
       </c>
       <c r="J310" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K310" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L310">
         <v>80123101</v>
@@ -15620,7 +15633,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="311" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" t="str">
         <f>_xlfn.XLOOKUP(I311,Lookup!A:A,Lookup!B:B)</f>
         <v>LG</v>
@@ -15649,10 +15662,10 @@
         <v>323</v>
       </c>
       <c r="J311" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K311" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L311">
         <v>90123101</v>
@@ -15664,7 +15677,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="312" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" t="str">
         <f>_xlfn.XLOOKUP(I312,Lookup!A:A,Lookup!B:B)</f>
         <v>LG</v>
@@ -15693,10 +15706,10 @@
         <v>323</v>
       </c>
       <c r="J312" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K312" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L312">
         <v>81123101</v>
@@ -15708,7 +15721,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="313" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" t="str">
         <f>_xlfn.XLOOKUP(I313,Lookup!A:A,Lookup!B:B)</f>
         <v>LG</v>
@@ -15734,10 +15747,10 @@
         <v>323</v>
       </c>
       <c r="J313" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K313" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L313">
         <v>80123101</v>
@@ -15749,7 +15762,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="314" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" t="str">
         <f>_xlfn.XLOOKUP(I314,Lookup!A:A,Lookup!B:B)</f>
         <v>LG</v>
@@ -15775,10 +15788,10 @@
         <v>323</v>
       </c>
       <c r="J314" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K314" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L314">
         <v>80123101</v>
@@ -15790,7 +15803,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="315" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" t="str">
         <f>_xlfn.XLOOKUP(I315,Lookup!A:A,Lookup!B:B)</f>
         <v>LG</v>
@@ -15816,10 +15829,10 @@
         <v>323</v>
       </c>
       <c r="J315" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K315" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L315">
         <v>80123101</v>
@@ -15831,7 +15844,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" t="str">
         <f>_xlfn.XLOOKUP(I316,Lookup!A:A,Lookup!B:B)</f>
         <v>LG</v>
@@ -15857,10 +15870,10 @@
         <v>323</v>
       </c>
       <c r="J316" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K316" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L316">
         <v>80123101</v>
@@ -15872,7 +15885,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="317" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" t="str">
         <f>_xlfn.XLOOKUP(I317,Lookup!A:A,Lookup!B:B)</f>
         <v>LG</v>
@@ -15898,10 +15911,10 @@
         <v>323</v>
       </c>
       <c r="J317" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K317" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L317">
         <v>80123101</v>
@@ -15913,7 +15926,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" t="str">
         <f>_xlfn.XLOOKUP(I318,Lookup!A:A,Lookup!B:B)</f>
         <v>LG</v>
@@ -15933,16 +15946,16 @@
         <v>333</v>
       </c>
       <c r="F318" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I318" t="s">
         <v>323</v>
       </c>
       <c r="J318" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K318" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L318">
         <v>80123101</v>
@@ -15950,8 +15963,11 @@
       <c r="M318">
         <v>61071005</v>
       </c>
-    </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R318" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="319" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" t="str">
         <f>_xlfn.XLOOKUP(I319,Lookup!A:A,Lookup!B:B)</f>
         <v>LG</v>
@@ -15980,10 +15996,10 @@
         <v>323</v>
       </c>
       <c r="J319" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K319" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L319">
         <v>80123101</v>
@@ -15992,7 +16008,7 @@
         <v>61071099</v>
       </c>
     </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" t="str">
         <f>_xlfn.XLOOKUP(I320,Lookup!A:A,Lookup!B:B)</f>
         <v>LG</v>
@@ -16021,10 +16037,10 @@
         <v>323</v>
       </c>
       <c r="J320" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K320" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L320">
         <v>81123101</v>
@@ -16033,7 +16049,7 @@
         <v>61071099</v>
       </c>
     </row>
-    <row r="321" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" t="str">
         <f>_xlfn.XLOOKUP(I321,Lookup!A:A,Lookup!B:B)</f>
         <v>LG</v>
@@ -16059,10 +16075,10 @@
         <v>323</v>
       </c>
       <c r="J321" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K321" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L321">
         <v>80123101</v>
@@ -16074,7 +16090,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="322" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:18" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" t="str">
         <f>_xlfn.XLOOKUP(I322,Lookup!A:A,Lookup!B:B)</f>
         <v>LG</v>
@@ -16100,10 +16116,10 @@
         <v>323</v>
       </c>
       <c r="J322" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K322" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L322">
         <v>90123101</v>
@@ -16115,7 +16131,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="323" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" t="str">
         <f>_xlfn.XLOOKUP(I323,Lookup!A:A,Lookup!B:B)</f>
         <v>LG</v>
@@ -16141,10 +16157,10 @@
         <v>323</v>
       </c>
       <c r="J323" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K323" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L323">
         <v>90122101</v>
@@ -16156,7 +16172,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="324" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" t="str">
         <f>_xlfn.XLOOKUP(I324,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -16184,10 +16200,10 @@
         <v>290</v>
       </c>
       <c r="J324" s="5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K324" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="L324">
         <v>81111204</v>
@@ -16196,7 +16212,7 @@
         <v>52091102</v>
       </c>
     </row>
-    <row r="325" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" t="str">
         <f>_xlfn.XLOOKUP(I325,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -16225,10 +16241,10 @@
         <v>290</v>
       </c>
       <c r="J325" s="5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K325" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="L325">
         <v>90111204</v>
@@ -16237,7 +16253,7 @@
         <v>61091102</v>
       </c>
     </row>
-    <row r="326" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" t="str">
         <f>_xlfn.XLOOKUP(I326,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -16266,10 +16282,10 @@
         <v>290</v>
       </c>
       <c r="J326" s="5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K326" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="L326">
         <v>80111204</v>
@@ -16278,7 +16294,7 @@
         <v>61091102</v>
       </c>
     </row>
-    <row r="327" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:18" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" t="str">
         <f>_xlfn.XLOOKUP(I327,Lookup!A:A,Lookup!B:B)</f>
         <v>CF</v>
@@ -16304,10 +16320,10 @@
         <v>290</v>
       </c>
       <c r="J327" s="5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K327" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="L327">
         <v>81134102</v>
@@ -16316,10 +16332,10 @@
         <v>52952101</v>
       </c>
       <c r="R327" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.35">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="328" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" t="str">
         <f>_xlfn.XLOOKUP(I328,Lookup!A:A,Lookup!B:B)</f>
         <v>OM</v>
@@ -16344,10 +16360,10 @@
         <v>300</v>
       </c>
       <c r="J328" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K328" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="L328">
         <v>81319101</v>
@@ -16359,7 +16375,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="329" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" t="str">
         <f>_xlfn.XLOOKUP(I329,Lookup!A:A,Lookup!B:B)</f>
         <v>OM</v>
@@ -16385,10 +16401,10 @@
         <v>300</v>
       </c>
       <c r="J329" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K329" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="L329">
         <v>81319101</v>
@@ -16400,7 +16416,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="330" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" t="str">
         <f>_xlfn.XLOOKUP(I330,Lookup!A:A,Lookup!B:B)</f>
         <v>OM</v>
@@ -16426,10 +16442,10 @@
         <v>300</v>
       </c>
       <c r="J330" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K330" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="L330">
         <v>81319101</v>
@@ -16444,7 +16460,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="331" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" t="str">
         <f>_xlfn.XLOOKUP(I331,Lookup!A:A,Lookup!B:B)</f>
         <v>OM</v>
@@ -16470,10 +16486,10 @@
         <v>300</v>
       </c>
       <c r="J331" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K331" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="L331">
         <v>81319101</v>
@@ -16485,7 +16501,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" t="str">
         <f>_xlfn.XLOOKUP(I332,Lookup!A:A,Lookup!B:B)</f>
         <v>OM</v>
@@ -16511,10 +16527,10 @@
         <v>300</v>
       </c>
       <c r="J332" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K332" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="L332">
         <v>81319101</v>
@@ -16526,7 +16542,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="333" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" t="str">
         <f>_xlfn.XLOOKUP(I333,Lookup!A:A,Lookup!B:B)</f>
         <v>OM</v>
@@ -16552,10 +16568,10 @@
         <v>300</v>
       </c>
       <c r="J333" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K333" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="L333">
         <v>81319101</v>
@@ -16567,7 +16583,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="334" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" t="str">
         <f>_xlfn.XLOOKUP(I334,Lookup!A:A,Lookup!B:B)</f>
         <v>OM</v>
@@ -16593,10 +16609,10 @@
         <v>300</v>
       </c>
       <c r="J334" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K334" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="L334">
         <v>81319101</v>
@@ -16608,7 +16624,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="335" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" t="str">
         <f>_xlfn.XLOOKUP(I335,Lookup!A:A,Lookup!B:B)</f>
         <v>OM</v>
@@ -16634,10 +16650,10 @@
         <v>300</v>
       </c>
       <c r="J335" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K335" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="L335">
         <v>81319101</v>
@@ -16649,7 +16665,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="336" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" t="str">
         <f>_xlfn.XLOOKUP(I336,Lookup!A:A,Lookup!B:B)</f>
         <v>PR</v>
@@ -16669,16 +16685,16 @@
         <v>264</v>
       </c>
       <c r="F336" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="I336" t="s">
         <v>350</v>
       </c>
       <c r="J336" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K336" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="L336">
         <v>80133103</v>
@@ -16688,7 +16704,7 @@
       </c>
       <c r="R336" s="5"/>
     </row>
-    <row r="337" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:18" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" t="str">
         <f>_xlfn.XLOOKUP(I337,Lookup!A:A,Lookup!B:B)</f>
         <v>PR</v>
@@ -16716,10 +16732,10 @@
         <v>350</v>
       </c>
       <c r="J337" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K337" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="L337">
         <v>81133103</v>
@@ -16731,7 +16747,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="338" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:18" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" t="str">
         <f>_xlfn.XLOOKUP(I338,Lookup!A:A,Lookup!B:B)</f>
         <v>PR</v>
@@ -16760,10 +16776,10 @@
         <v>350</v>
       </c>
       <c r="J338" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K338" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="L338">
         <v>80133103</v>
@@ -16775,7 +16791,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="339" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" t="str">
         <f>_xlfn.XLOOKUP(I339,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -16804,10 +16820,10 @@
         <v>86</v>
       </c>
       <c r="J339" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K339" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L339">
         <v>80133102</v>
@@ -16819,7 +16835,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="340" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" t="str">
         <f>_xlfn.XLOOKUP(I340,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -16849,10 +16865,10 @@
         <v>86</v>
       </c>
       <c r="J340" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K340" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L340">
         <v>81133102</v>
@@ -16860,8 +16876,11 @@
       <c r="M340">
         <v>52071104</v>
       </c>
-    </row>
-    <row r="341" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R340" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="341" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" t="str">
         <f>_xlfn.XLOOKUP(I341,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -16891,10 +16910,10 @@
         <v>86</v>
       </c>
       <c r="J341" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K341" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L341">
         <v>90133102</v>
@@ -16902,8 +16921,11 @@
       <c r="M341">
         <v>52071104</v>
       </c>
-    </row>
-    <row r="342" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R341" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="342" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" t="str">
         <f>_xlfn.XLOOKUP(I342,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -16923,7 +16945,7 @@
         <v>247</v>
       </c>
       <c r="F342" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G342"/>
       <c r="H342"/>
@@ -16931,10 +16953,10 @@
         <v>86</v>
       </c>
       <c r="J342" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K342" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L342">
         <v>80133102</v>
@@ -16946,7 +16968,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="343" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" t="str">
         <f>_xlfn.XLOOKUP(I343,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -16966,7 +16988,7 @@
         <v>247</v>
       </c>
       <c r="F343" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G343" t="s">
         <v>220</v>
@@ -16976,10 +16998,10 @@
         <v>86</v>
       </c>
       <c r="J343" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K343" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L343">
         <v>80111101</v>
@@ -16991,7 +17013,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="344" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" t="str">
         <f>_xlfn.XLOOKUP(I344,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -17011,7 +17033,7 @@
         <v>247</v>
       </c>
       <c r="F344" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G344" t="s">
         <v>219</v>
@@ -17021,10 +17043,10 @@
         <v>86</v>
       </c>
       <c r="J344" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K344" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L344">
         <v>81111101</v>
@@ -17036,7 +17058,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="345" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" t="str">
         <f>_xlfn.XLOOKUP(I345,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -17056,7 +17078,7 @@
         <v>247</v>
       </c>
       <c r="F345" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G345" t="s">
         <v>221</v>
@@ -17066,10 +17088,10 @@
         <v>86</v>
       </c>
       <c r="J345" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K345" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L345">
         <v>90111101</v>
@@ -17081,7 +17103,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="346" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" t="str">
         <f>_xlfn.XLOOKUP(I346,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -17101,7 +17123,7 @@
         <v>247</v>
       </c>
       <c r="F346" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G346" t="s">
         <v>221</v>
@@ -17111,10 +17133,10 @@
         <v>86</v>
       </c>
       <c r="J346" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K346" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L346">
         <v>90111101</v>
@@ -17126,7 +17148,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="347" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" t="str">
         <f>_xlfn.XLOOKUP(I347,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -17146,7 +17168,7 @@
         <v>247</v>
       </c>
       <c r="F347" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G347" t="s">
         <v>220</v>
@@ -17156,10 +17178,10 @@
         <v>86</v>
       </c>
       <c r="J347" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K347" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L347">
         <v>80111101</v>
@@ -17171,7 +17193,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="348" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" t="str">
         <f>_xlfn.XLOOKUP(I348,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -17191,7 +17213,7 @@
         <v>247</v>
       </c>
       <c r="F348" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G348" t="s">
         <v>219</v>
@@ -17201,10 +17223,10 @@
         <v>86</v>
       </c>
       <c r="J348" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K348" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L348">
         <v>81111101</v>
@@ -17216,7 +17238,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="349" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" t="str">
         <f>_xlfn.XLOOKUP(I349,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -17236,7 +17258,7 @@
         <v>247</v>
       </c>
       <c r="F349" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G349" t="s">
         <v>221</v>
@@ -17246,10 +17268,10 @@
         <v>86</v>
       </c>
       <c r="J349" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K349" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L349">
         <v>90111101</v>
@@ -17261,7 +17283,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="350" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" t="str">
         <f>_xlfn.XLOOKUP(I350,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -17281,7 +17303,7 @@
         <v>247</v>
       </c>
       <c r="F350" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G350" t="s">
         <v>221</v>
@@ -17291,10 +17313,10 @@
         <v>86</v>
       </c>
       <c r="J350" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K350" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L350">
         <v>90111101</v>
@@ -17306,7 +17328,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="351" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" t="str">
         <f>_xlfn.XLOOKUP(I351,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -17326,7 +17348,7 @@
         <v>247</v>
       </c>
       <c r="F351" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G351" t="s">
         <v>219</v>
@@ -17336,10 +17358,10 @@
         <v>86</v>
       </c>
       <c r="J351" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K351" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L351">
         <v>81111101</v>
@@ -17351,7 +17373,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="352" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" t="str">
         <f>_xlfn.XLOOKUP(I352,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -17371,7 +17393,7 @@
         <v>247</v>
       </c>
       <c r="F352" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G352" t="s">
         <v>221</v>
@@ -17381,10 +17403,10 @@
         <v>86</v>
       </c>
       <c r="J352" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K352" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L352">
         <v>90111101</v>
@@ -17396,7 +17418,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="353" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" t="str">
         <f>_xlfn.XLOOKUP(I353,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -17416,7 +17438,7 @@
         <v>247</v>
       </c>
       <c r="F353" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G353" t="s">
         <v>221</v>
@@ -17426,10 +17448,10 @@
         <v>86</v>
       </c>
       <c r="J353" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K353" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L353">
         <v>90111101</v>
@@ -17441,7 +17463,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="354" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" t="str">
         <f>_xlfn.XLOOKUP(I354,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -17461,7 +17483,7 @@
         <v>247</v>
       </c>
       <c r="F354" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G354" t="s">
         <v>220</v>
@@ -17471,10 +17493,10 @@
         <v>86</v>
       </c>
       <c r="J354" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K354" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L354">
         <v>80133102</v>
@@ -17486,7 +17508,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="355" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" t="str">
         <f>_xlfn.XLOOKUP(I355,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -17506,7 +17528,7 @@
         <v>247</v>
       </c>
       <c r="F355" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G355" t="s">
         <v>219</v>
@@ -17516,10 +17538,10 @@
         <v>86</v>
       </c>
       <c r="J355" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K355" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L355">
         <v>81133102</v>
@@ -17531,7 +17553,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="356" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" t="str">
         <f>_xlfn.XLOOKUP(I356,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -17551,7 +17573,7 @@
         <v>247</v>
       </c>
       <c r="F356" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G356" t="s">
         <v>221</v>
@@ -17561,10 +17583,10 @@
         <v>86</v>
       </c>
       <c r="J356" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K356" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L356">
         <v>90133102</v>
@@ -17576,7 +17598,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="357" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" t="str">
         <f>_xlfn.XLOOKUP(I357,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -17596,16 +17618,16 @@
         <v>247</v>
       </c>
       <c r="F357" s="5" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I357" t="s">
         <v>86</v>
       </c>
       <c r="J357" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K357" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L357">
         <v>90133102</v>
@@ -17613,8 +17635,11 @@
       <c r="M357">
         <v>52952101</v>
       </c>
-    </row>
-    <row r="358" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R357" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="358" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" t="str">
         <f>_xlfn.XLOOKUP(I358,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -17634,7 +17659,7 @@
         <v>247</v>
       </c>
       <c r="F358" s="5" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G358" s="5" t="s">
         <v>220</v>
@@ -17643,10 +17668,10 @@
         <v>86</v>
       </c>
       <c r="J358" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K358" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L358">
         <v>80111101</v>
@@ -17654,8 +17679,11 @@
       <c r="M358">
         <v>52031101</v>
       </c>
-    </row>
-    <row r="359" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R358" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="359" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" t="str">
         <f>_xlfn.XLOOKUP(I359,Lookup!A:A,Lookup!B:B)</f>
         <v>TX</v>
@@ -17675,7 +17703,7 @@
         <v>247</v>
       </c>
       <c r="F359" s="5" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G359" s="5" t="s">
         <v>221</v>
@@ -17684,10 +17712,10 @@
         <v>86</v>
       </c>
       <c r="J359" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K359" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L359">
         <v>81111101</v>
@@ -17695,8 +17723,11 @@
       <c r="M359">
         <v>52031101</v>
       </c>
-    </row>
-    <row r="360" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R359" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="360" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" t="str">
         <f>_xlfn.XLOOKUP(I360,Lookup!A:A,Lookup!B:B)</f>
         <v>TS</v>
@@ -17716,16 +17747,16 @@
         <v>325</v>
       </c>
       <c r="F360" s="5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="I360" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J360" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K360" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="L360">
         <v>80215106</v>
@@ -17733,9 +17764,18 @@
       <c r="M360">
         <v>61071004</v>
       </c>
+      <c r="R360" t="s">
+        <v>86</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:R360" xr:uid="{0B1226CB-0107-4D8F-A599-9B58ED89F844}"/>
+  <autoFilter ref="A2:R360" xr:uid="{0B1226CB-0107-4D8F-A599-9B58ED89F844}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="Administrative Services"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="J225:J235 H2:H202 H209:H1048576 J158:J213 K50:K80 J36:K49">
     <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
@@ -17755,10 +17795,10 @@
   <sheetData>
     <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.35">
@@ -17766,15 +17806,15 @@
         <v>351</v>
       </c>
       <c r="B3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.35">
@@ -17782,15 +17822,15 @@
         <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.35">
@@ -17798,7 +17838,7 @@
         <v>323</v>
       </c>
       <c r="B7" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.35">
@@ -17806,7 +17846,7 @@
         <v>290</v>
       </c>
       <c r="B8" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.35">
@@ -17814,15 +17854,15 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.35">
@@ -17830,7 +17870,7 @@
         <v>165</v>
       </c>
       <c r="B11" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.35">
@@ -17838,7 +17878,7 @@
         <v>300</v>
       </c>
       <c r="B12" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.35">
@@ -17846,15 +17886,15 @@
         <v>350</v>
       </c>
       <c r="B13" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B14" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>

--- a/Budgeting System_Expense Line Items.xlsx
+++ b/Budgeting System_Expense Line Items.xlsx
@@ -3889,6 +3889,11 @@
       <c r="F38" s="5" t="s">
         <v>502</v>
       </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>OCC</t>
+        </is>
+      </c>
       <c r="I38" t="s">
         <v>443</v>
       </c>
@@ -3930,6 +3935,11 @@
       <c r="F39" s="5" t="s">
         <v>502</v>
       </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>OCLP</t>
+        </is>
+      </c>
       <c r="I39" t="s">
         <v>443</v>
       </c>
@@ -10839,6 +10849,11 @@
       <c r="F195" s="5" t="s">
         <v>341</v>
       </c>
+      <c r="G195" s="5" t="inlineStr">
+        <is>
+          <t>OCC</t>
+        </is>
+      </c>
       <c r="I195" t="s">
         <v>84</v>
       </c>
@@ -10880,6 +10895,11 @@
       <c r="F196" s="5" t="s">
         <v>341</v>
       </c>
+      <c r="G196" s="5" t="inlineStr">
+        <is>
+          <t>OCLP</t>
+        </is>
+      </c>
       <c r="I196" t="s">
         <v>84</v>
       </c>
@@ -10921,6 +10941,11 @@
       <c r="F197" s="5" t="s">
         <v>341</v>
       </c>
+      <c r="G197" s="5" t="inlineStr">
+        <is>
+          <t>OLC</t>
+        </is>
+      </c>
       <c r="I197" t="s">
         <v>84</v>
       </c>
@@ -11367,6 +11392,11 @@
       <c r="F207" s="5" t="s">
         <v>342</v>
       </c>
+      <c r="G207" s="5" t="inlineStr">
+        <is>
+          <t>OCC</t>
+        </is>
+      </c>
       <c r="I207" t="s">
         <v>84</v>
       </c>
@@ -11408,6 +11438,11 @@
       <c r="F208" s="5" t="s">
         <v>342</v>
       </c>
+      <c r="G208" s="5" t="inlineStr">
+        <is>
+          <t>OCLP</t>
+        </is>
+      </c>
       <c r="I208" t="s">
         <v>84</v>
       </c>
@@ -11448,6 +11483,11 @@
       </c>
       <c r="F209" s="5" t="s">
         <v>342</v>
+      </c>
+      <c r="G209" s="5" t="inlineStr">
+        <is>
+          <t>OLC</t>
+        </is>
       </c>
       <c r="I209" t="s">
         <v>84</v>

--- a/Budgeting System_Expense Line Items.xlsx
+++ b/Budgeting System_Expense Line Items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jumalonpvp\Downloads\Budgeting System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22C5CD5-4330-4943-873D-82AB26DC2A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D336090E-2934-4E30-BA17-06665BAB9329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7D30BD04-AED0-48C4-A0F0-DC51EF4C24C2}"/>
   </bookViews>
@@ -3889,10 +3889,8 @@
       <c r="F38" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>OCC</t>
-        </is>
+      <c r="G38" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="I38" t="s">
         <v>443</v>
@@ -3935,10 +3933,8 @@
       <c r="F39" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>OCLP</t>
-        </is>
+      <c r="G39" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="I39" t="s">
         <v>443</v>
@@ -10849,10 +10845,8 @@
       <c r="F195" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="G195" s="5" t="inlineStr">
-        <is>
-          <t>OCC</t>
-        </is>
+      <c r="G195" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="I195" t="s">
         <v>84</v>
@@ -10895,10 +10889,8 @@
       <c r="F196" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="G196" s="5" t="inlineStr">
-        <is>
-          <t>OCLP</t>
-        </is>
+      <c r="G196" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="I196" t="s">
         <v>84</v>
@@ -10941,10 +10933,8 @@
       <c r="F197" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="G197" s="5" t="inlineStr">
-        <is>
-          <t>OLC</t>
-        </is>
+      <c r="G197" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="I197" t="s">
         <v>84</v>
@@ -11392,10 +11382,8 @@
       <c r="F207" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="G207" s="5" t="inlineStr">
-        <is>
-          <t>OCC</t>
-        </is>
+      <c r="G207" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="I207" t="s">
         <v>84</v>
@@ -11438,10 +11426,8 @@
       <c r="F208" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="G208" s="5" t="inlineStr">
-        <is>
-          <t>OCLP</t>
-        </is>
+      <c r="G208" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="I208" t="s">
         <v>84</v>
@@ -11484,10 +11470,8 @@
       <c r="F209" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="G209" s="5" t="inlineStr">
-        <is>
-          <t>OLC</t>
-        </is>
+      <c r="G209" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="I209" t="s">
         <v>84</v>
@@ -16529,9 +16513,6 @@
       <c r="M329">
         <v>52111102</v>
       </c>
-      <c r="R329" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="330" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A330" t="str">
@@ -16570,9 +16551,6 @@
       <c r="M330">
         <v>52111102</v>
       </c>
-      <c r="R330" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="331" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A331" t="str">
@@ -16614,9 +16592,6 @@
       <c r="N331" t="s">
         <v>249</v>
       </c>
-      <c r="R331" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="332" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A332" t="str">
@@ -16655,9 +16630,6 @@
       <c r="M332">
         <v>52111101</v>
       </c>
-      <c r="R332" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="333" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A333" t="str">
@@ -16696,9 +16668,6 @@
       <c r="M333">
         <v>52061103</v>
       </c>
-      <c r="R333" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="334" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A334" t="str">
@@ -16737,9 +16706,6 @@
       <c r="M334">
         <v>52061101</v>
       </c>
-      <c r="R334" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="335" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A335" t="str">
@@ -16778,9 +16744,6 @@
       <c r="M335">
         <v>52061103</v>
       </c>
-      <c r="R335" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="336" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A336" t="str">
@@ -16818,9 +16781,6 @@
       </c>
       <c r="M336">
         <v>52061105</v>
-      </c>
-      <c r="R336" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="337" spans="1:18" x14ac:dyDescent="0.35">
